--- a/config/DrofusConfirmedRoutes.xlsx
+++ b/config/DrofusConfirmedRoutes.xlsx
@@ -196,8 +196,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Exceptions" displayName="Exceptions" ref="A1:Z54" headerRowCount="1">
-  <autoFilter ref="A1:Z54"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Exceptions" displayName="Exceptions" ref="A1:Z18" headerRowCount="1">
+  <autoFilter ref="A1:Z18"/>
   <tableColumns count="26">
     <tableColumn id="1" name="Strekk"/>
     <tableColumn id="2" name="Rolle"/>
@@ -558,7 +558,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>D:\Revit\Python\Revit_BIM_Agent\logs\reports\BAS batch 20261016_134717 confirmed-snapshot.tsv</t>
+          <t>D:\Revit\Python\Revit_BIM_Agent\logs\reports\BAS strekk samordning 20261016_1450 remaining Verify confirmed.tsv</t>
         </is>
       </c>
     </row>
@@ -570,7 +570,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-16T13:51:03</t>
+          <t>2026-10-16T14:57:12</t>
         </is>
       </c>
     </row>
@@ -657,7 +657,7 @@
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="55" customWidth="1" min="9" max="9"/>
   </cols>
@@ -750,7 +750,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Kontrollerte felt samsvarer i snapshot | Merke/sekvens avviker fra representant</t>
+          <t>Kontrollerte felt samsvarer i snapshot</t>
         </is>
       </c>
     </row>
@@ -795,7 +795,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Kontrollerte felt samsvarer i snapshot | Merke/sekvens avviker fra representant; Rominfo avviker – avklar</t>
+          <t>Kontrollerte felt samsvarer i snapshot | Rominfo avviker – avklar</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Kontrollerte felt samsvarer i snapshot | Merke/sekvens avviker fra representant</t>
+          <t>Kontrollerte felt samsvarer i snapshot</t>
         </is>
       </c>
     </row>
@@ -885,7 +885,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Merke/sekvens avviker fra representant | Kontrollerte felt samsvarer i snapshot</t>
+          <t>Kontrollerte felt samsvarer i snapshot</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Kontrollerte felt samsvarer i snapshot | Merke/sekvens avviker fra representant</t>
+          <t>Kontrollerte felt samsvarer i snapshot</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Kontrollerte felt samsvarer i snapshot | Mangler gyldig merke/sekvens; Merke/sekvens avviker fra representant; Mangler rominfo</t>
+          <t>Kontrollerte felt samsvarer i snapshot | Mangler rominfo</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Merke/sekvens avviker fra representant | Kontrollerte felt samsvarer i snapshot</t>
+          <t>Kontrollerte felt samsvarer i snapshot</t>
         </is>
       </c>
     </row>
@@ -1065,7 +1065,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Merke/sekvens avviker fra representant | Kontrollerte felt samsvarer i snapshot | Mangler gyldig merke/sekvens; Merke/sekvens avviker fra representant; Mangler rominfo</t>
+          <t>Kontrollerte felt samsvarer i snapshot | Mangler rominfo</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Kontrollerte felt samsvarer i snapshot | Merke/sekvens avviker fra representant; Rominfo avviker – avklar</t>
+          <t>Kontrollerte felt samsvarer i snapshot | Rominfo avviker – avklar</t>
         </is>
       </c>
     </row>
@@ -1138,14 +1138,24 @@
           <t>808629</t>
         </is>
       </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>BYG201-460-KAF-129</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Error: Value cannot be null. (Parameter 'input')</t>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>E3S.01</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Representant mangler gyldig merkekilde; Rominfo avviker – avklar | Mangler gyldig merke/sekvens; Representant mangler gyldig merkekilde; Mangler rominfo</t>
+          <t>Kontrollerte felt samsvarer i snapshot</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1200,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Merke/sekvens avviker fra representant | Kontrollerte felt samsvarer i snapshot</t>
+          <t>Kontrollerte felt samsvarer i snapshot</t>
         </is>
       </c>
     </row>
@@ -1235,7 +1245,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Merke/sekvens avviker fra representant | Kontrollerte felt samsvarer i snapshot</t>
+          <t>Kontrollerte felt samsvarer i snapshot</t>
         </is>
       </c>
     </row>
@@ -1263,14 +1273,24 @@
           <t>808278</t>
         </is>
       </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>BYG201-460-KAF-011</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Error: Value cannot be null. (Parameter 'input')</t>
+          <t>011</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>C3S.02</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Mangler gyldig merke/sekvens; Representant mangler gyldig merkekilde; Mangler rominfo</t>
+          <t>Kontrollerte felt samsvarer i snapshot | Mangler rominfo</t>
         </is>
       </c>
     </row>
@@ -1315,7 +1335,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Kontrollerte felt samsvarer i snapshot | Mangler gyldig merke/sekvens; Merke/sekvens avviker fra representant; Mangler rominfo</t>
+          <t>Kontrollerte felt samsvarer i snapshot | Mangler rominfo</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1380,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Merke/sekvens avviker fra representant | Kontrollerte felt samsvarer i snapshot</t>
+          <t>Kontrollerte felt samsvarer i snapshot</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1425,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Merke/sekvens avviker fra representant | Kontrollerte felt samsvarer i snapshot</t>
+          <t>Kontrollerte felt samsvarer i snapshot</t>
         </is>
       </c>
     </row>
@@ -1450,7 +1470,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Merke/sekvens avviker fra representant | Kontrollerte felt samsvarer i snapshot</t>
+          <t>Kontrollerte felt samsvarer i snapshot</t>
         </is>
       </c>
     </row>
@@ -1495,7 +1515,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Merke/sekvens avviker fra representant | Kontrollerte felt samsvarer i snapshot</t>
+          <t>Kontrollerte felt samsvarer i snapshot</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1560,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Merke/sekvens avviker fra representant | Kontrollerte felt samsvarer i snapshot</t>
+          <t>Kontrollerte felt samsvarer i snapshot</t>
         </is>
       </c>
     </row>
@@ -1585,7 +1605,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Merke/sekvens avviker fra representant | Kontrollerte felt samsvarer i snapshot</t>
+          <t>Kontrollerte felt samsvarer i snapshot</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1650,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Merke/sekvens avviker fra representant | Kontrollerte felt samsvarer i snapshot</t>
+          <t>Kontrollerte felt samsvarer i snapshot</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1695,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Merke/sekvens avviker fra representant | Merke/sekvens avviker fra representant; Rominfo avviker – avklar | Kontrollerte felt samsvarer i snapshot</t>
+          <t>Kontrollerte felt samsvarer i snapshot | Rominfo avviker – avklar</t>
         </is>
       </c>
     </row>
@@ -1720,7 +1740,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Merke/sekvens avviker fra representant | Kontrollerte felt samsvarer i snapshot</t>
+          <t>Kontrollerte felt samsvarer i snapshot</t>
         </is>
       </c>
     </row>
@@ -1756,14 +1776,14 @@
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="20" customWidth="1" min="15" max="15"/>
-    <col width="50" customWidth="1" min="16" max="16"/>
+    <col width="15" customWidth="1" min="16" max="16"/>
     <col width="14" customWidth="1" min="17" max="17"/>
     <col width="14" customWidth="1" min="18" max="18"/>
     <col width="25" customWidth="1" min="19" max="19"/>
     <col width="20" customWidth="1" min="20" max="20"/>
-    <col width="50" customWidth="1" min="21" max="21"/>
+    <col width="21" customWidth="1" min="21" max="21"/>
     <col width="23" customWidth="1" min="22" max="22"/>
-    <col width="55" customWidth="1" min="23" max="23"/>
+    <col width="40" customWidth="1" min="23" max="23"/>
     <col width="54" customWidth="1" min="24" max="24"/>
     <col width="47" customWidth="1" min="25" max="25"/>
     <col width="14" customWidth="1" min="26" max="26"/>
@@ -2079,12 +2099,12 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>BYG203-460-KAF-069</t>
+          <t>BYG203-460-KAF-072</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>069</t>
+          <t>072</t>
         </is>
       </c>
       <c r="Q3" t="n">
@@ -2117,7 +2137,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Merke/sekvens avviker fra representant</t>
+          <t>Kontrollerte felt samsvarer i snapshot</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -2309,12 +2329,12 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>BYG201-460-KAF-312</t>
+          <t>BYG201-460-KAF-153</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>153</t>
         </is>
       </c>
       <c r="Q5" t="n">
@@ -2347,7 +2367,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Merke/sekvens avviker fra representant; Rominfo avviker – avklar</t>
+          <t>Rominfo avviker – avklar</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2424,12 +2444,12 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>BYG201-460-KAF-314</t>
+          <t>BYG201-460-KAF-153</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>153</t>
         </is>
       </c>
       <c r="Q6" t="n">
@@ -2462,7 +2482,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Merke/sekvens avviker fra representant; Rominfo avviker – avklar</t>
+          <t>Rominfo avviker – avklar</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2539,12 +2559,12 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>BYG201-460-KAF-095</t>
+          <t>BYG201-460-KAF-153</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>095</t>
+          <t>153</t>
         </is>
       </c>
       <c r="Q7" t="n">
@@ -2577,7 +2597,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Merke/sekvens avviker fra representant; Rominfo avviker – avklar</t>
+          <t>Rominfo avviker – avklar</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -2769,12 +2789,12 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>BYG201-460-KAF-165</t>
+          <t>BYG201-460-KAF-164</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>164</t>
         </is>
       </c>
       <c r="Q9" t="n">
@@ -2807,7 +2827,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Merke/sekvens avviker fra representant</t>
+          <t>Kontrollerte felt samsvarer i snapshot</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -2884,12 +2904,12 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>BYG201-460-KAF-171</t>
+          <t>BYG201-460-KAF-172</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>172</t>
         </is>
       </c>
       <c r="Q10" t="n">
@@ -2922,7 +2942,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Merke/sekvens avviker fra representant</t>
+          <t>Kontrollerte felt samsvarer i snapshot</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -3114,12 +3134,12 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>BYG201-460-KAF-173</t>
+          <t>BYG201-460-KAF-172</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>172</t>
         </is>
       </c>
       <c r="Q12" t="n">
@@ -3152,7 +3172,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Merke/sekvens avviker fra representant</t>
+          <t>Kontrollerte felt samsvarer i snapshot</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -3344,12 +3364,12 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>BYG201-460-KAF-231</t>
+          <t>BYG201-460-KAF-174</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>174</t>
         </is>
       </c>
       <c r="Q14" t="n">
@@ -3382,7 +3402,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>Merke/sekvens avviker fra representant</t>
+          <t>Kontrollerte felt samsvarer i snapshot</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -3459,12 +3479,12 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>BYG201-460-KAF-232</t>
+          <t>BYG201-460-KAF-174</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>174</t>
         </is>
       </c>
       <c r="Q15" t="n">
@@ -3497,7 +3517,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>Merke/sekvens avviker fra representant</t>
+          <t>Kontrollerte felt samsvarer i snapshot</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -3574,12 +3594,12 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>BYG201-460-KAF-278</t>
+          <t>BYG201-460-KAF-174</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>174</t>
         </is>
       </c>
       <c r="Q16" t="n">
@@ -3612,7 +3632,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Merke/sekvens avviker fra representant</t>
+          <t>Kontrollerte felt samsvarer i snapshot</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -3797,9 +3817,14 @@
           <t>True</t>
         </is>
       </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>P14-460-KAF-041</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Error: Value cannot be null. (Parameter 'input')</t>
+          <t>041</t>
         </is>
       </c>
       <c r="Q18" t="n">
@@ -3822,7 +3847,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Mangler gyldig merke/sekvens; Merke/sekvens avviker fra representant; Mangler rominfo</t>
+          <t>Mangler rominfo</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -3899,12 +3924,12 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>P14-460-KAF-022</t>
+          <t>P14-460-KAF-028</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>022</t>
+          <t>028</t>
         </is>
       </c>
       <c r="Q19" t="n">
@@ -3932,7 +3957,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Merke/sekvens avviker fra representant</t>
+          <t>Kontrollerte felt samsvarer i snapshot</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -4009,12 +4034,12 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>P14-460-KAF-024</t>
+          <t>P14-460-KAF-028</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>024</t>
+          <t>028</t>
         </is>
       </c>
       <c r="Q20" t="n">
@@ -4042,7 +4067,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>Merke/sekvens avviker fra representant</t>
+          <t>Kontrollerte felt samsvarer i snapshot</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -4119,12 +4144,12 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>P14-460-KAF-025</t>
+          <t>P14-460-KAF-028</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>028</t>
         </is>
       </c>
       <c r="Q21" t="n">
@@ -4152,7 +4177,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>Merke/sekvens avviker fra representant</t>
+          <t>Kontrollerte felt samsvarer i snapshot</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -4339,12 +4364,12 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>P14-460-KAF-029</t>
+          <t>P14-460-KAF-042</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>029</t>
+          <t>042</t>
         </is>
       </c>
       <c r="Q23" t="n">
@@ -4372,7 +4397,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>Merke/sekvens avviker fra representant</t>
+          <t>Kontrollerte felt samsvarer i snapshot</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -4557,9 +4582,14 @@
           <t>True</t>
         </is>
       </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>P14-460-KAF-042</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Error: Value cannot be null. (Parameter 'input')</t>
+          <t>042</t>
         </is>
       </c>
       <c r="Q25" t="n">
@@ -4582,7 +4612,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>Mangler gyldig merke/sekvens; Merke/sekvens avviker fra representant; Mangler rominfo</t>
+          <t>Mangler rominfo</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -4774,12 +4804,12 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>BYG202-460-KAF-415</t>
+          <t>BYG202-460-KAF-384</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>415</t>
+          <t>384</t>
         </is>
       </c>
       <c r="Q27" t="n">
@@ -4812,7 +4842,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>Merke/sekvens avviker fra representant; Rominfo avviker – avklar</t>
+          <t>Rominfo avviker – avklar</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -4889,12 +4919,12 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>BYG202-460-KAF-240</t>
+          <t>BYG202-460-KAF-384</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>384</t>
         </is>
       </c>
       <c r="Q28" t="n">
@@ -4927,7 +4957,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>Merke/sekvens avviker fra representant; Rominfo avviker – avklar</t>
+          <t>Rominfo avviker – avklar</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
@@ -5004,12 +5034,12 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>BYG201-460-KAF-222</t>
+          <t>BYG201-460-KAF-129</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>129</t>
         </is>
       </c>
       <c r="Q29" t="n">
@@ -5025,14 +5055,24 @@
           <t>Spor P8-P9 nord</t>
         </is>
       </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>BYG201-460-KAF-129</t>
+        </is>
+      </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>Error: Value cannot be null. (Parameter 'input')</t>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>E3S.01</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>Representant mangler gyldig merkekilde; Rominfo avviker – avklar</t>
+          <t>Kontrollerte felt samsvarer i snapshot</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
@@ -5109,12 +5149,12 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>BYG201-460-KAF-289</t>
+          <t>BYG201-460-KAF-129</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>129</t>
         </is>
       </c>
       <c r="Q30" t="n">
@@ -5130,14 +5170,24 @@
           <t>Spor P8-P9 nord</t>
         </is>
       </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>BYG201-460-KAF-129</t>
+        </is>
+      </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>Error: Value cannot be null. (Parameter 'input')</t>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>E3S.01</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>Representant mangler gyldig merkekilde; Rominfo avviker – avklar</t>
+          <t>Kontrollerte felt samsvarer i snapshot</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
@@ -5214,12 +5264,12 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>BYG201-460-KAF-290</t>
+          <t>BYG201-460-KAF-129</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>129</t>
         </is>
       </c>
       <c r="Q31" t="n">
@@ -5235,14 +5285,24 @@
           <t>Spor P8-P9 nord</t>
         </is>
       </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>BYG201-460-KAF-129</t>
+        </is>
+      </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>Error: Value cannot be null. (Parameter 'input')</t>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>E3S.01</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>Representant mangler gyldig merkekilde; Rominfo avviker – avklar</t>
+          <t>Kontrollerte felt samsvarer i snapshot</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
@@ -5317,22 +5377,47 @@
           <t>False</t>
         </is>
       </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>BYG201-460-KAF-129</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Error: Value cannot be null. (Parameter 'input')</t>
+          <t>129</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>2796</v>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>E3S.01</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>Spor P8-P9 nord</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>BYG201-460-KAF-129</t>
+        </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>Error: Value cannot be null. (Parameter 'input')</t>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>E3S.01</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>Mangler gyldig merke/sekvens; Representant mangler gyldig merkekilde; Mangler rominfo</t>
+          <t>Kontrollerte felt samsvarer i snapshot</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
@@ -5409,12 +5494,12 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>BYG203-460-KAF-071</t>
+          <t>BYG203-460-KAF-089</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>071</t>
+          <t>089</t>
         </is>
       </c>
       <c r="Q33" t="n">
@@ -5447,7 +5532,7 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>Merke/sekvens avviker fra representant</t>
+          <t>Kontrollerte felt samsvarer i snapshot</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
@@ -5524,12 +5609,12 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>BYG203-460-KAF-081</t>
+          <t>BYG203-460-KAF-089</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>081</t>
+          <t>089</t>
         </is>
       </c>
       <c r="Q34" t="n">
@@ -5562,7 +5647,7 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>Merke/sekvens avviker fra representant</t>
+          <t>Kontrollerte felt samsvarer i snapshot</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
@@ -5754,12 +5839,12 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>BYG201-460-KAF-158</t>
+          <t>BYG201-460-KAF-310</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>310</t>
         </is>
       </c>
       <c r="Q36" t="n">
@@ -5792,7 +5877,7 @@
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>Merke/sekvens avviker fra representant</t>
+          <t>Kontrollerte felt samsvarer i snapshot</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
@@ -5869,12 +5954,12 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>BYG201-460-KAF-309</t>
+          <t>BYG201-460-KAF-310</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>310</t>
         </is>
       </c>
       <c r="Q37" t="n">
@@ -5907,7 +5992,7 @@
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>Merke/sekvens avviker fra representant</t>
+          <t>Kontrollerte felt samsvarer i snapshot</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
@@ -6099,12 +6184,12 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>BYG201-460-KAF-129</t>
+          <t>BYG201-460-KAF-310</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>310</t>
         </is>
       </c>
       <c r="Q39" t="n">
@@ -6137,7 +6222,7 @@
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>Merke/sekvens avviker fra representant</t>
+          <t>Kontrollerte felt samsvarer i snapshot</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
@@ -6212,22 +6297,47 @@
           <t>False</t>
         </is>
       </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>BYG201-460-KAF-011</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Error: Value cannot be null. (Parameter 'input')</t>
+          <t>011</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3650</v>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>C3S.02</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>Nordvest 4</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>BYG201-460-KAF-011</t>
+        </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>Error: Value cannot be null. (Parameter 'input')</t>
+          <t>011</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>C3S.02</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>Mangler gyldig merke/sekvens; Representant mangler gyldig merkekilde; Mangler rominfo</t>
+          <t>Kontrollerte felt samsvarer i snapshot</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
@@ -6302,22 +6412,37 @@
           <t>True</t>
         </is>
       </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>BYG201-460-KAF-011</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Error: Value cannot be null. (Parameter 'input')</t>
+          <t>011</t>
         </is>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
       </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>BYG201-460-KAF-011</t>
+        </is>
+      </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>Error: Value cannot be null. (Parameter 'input')</t>
+          <t>011</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>C3S.02</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>Mangler gyldig merke/sekvens; Representant mangler gyldig merkekilde; Mangler rominfo</t>
+          <t>Mangler rominfo</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
@@ -6392,22 +6517,37 @@
           <t>True</t>
         </is>
       </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>BYG201-460-KAF-011</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Error: Value cannot be null. (Parameter 'input')</t>
+          <t>011</t>
         </is>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
       </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>BYG201-460-KAF-011</t>
+        </is>
+      </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>Error: Value cannot be null. (Parameter 'input')</t>
+          <t>011</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>C3S.02</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>Mangler gyldig merke/sekvens; Representant mangler gyldig merkekilde; Mangler rominfo</t>
+          <t>Mangler rominfo</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
@@ -6482,22 +6622,37 @@
           <t>True</t>
         </is>
       </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>BYG201-460-KAF-011</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Error: Value cannot be null. (Parameter 'input')</t>
+          <t>011</t>
         </is>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
       </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>BYG201-460-KAF-011</t>
+        </is>
+      </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>Error: Value cannot be null. (Parameter 'input')</t>
+          <t>011</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>C3S.02</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>Mangler gyldig merke/sekvens; Representant mangler gyldig merkekilde; Mangler rominfo</t>
+          <t>Mangler rominfo</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
@@ -6572,22 +6727,37 @@
           <t>True</t>
         </is>
       </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>BYG201-460-KAF-011</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Error: Value cannot be null. (Parameter 'input')</t>
+          <t>011</t>
         </is>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
       </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>BYG201-460-KAF-011</t>
+        </is>
+      </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>Error: Value cannot be null. (Parameter 'input')</t>
+          <t>011</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>C3S.02</t>
         </is>
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>Mangler gyldig merke/sekvens; Representant mangler gyldig merkekilde; Mangler rominfo</t>
+          <t>Mangler rominfo</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
@@ -6777,9 +6947,14 @@
           <t>True</t>
         </is>
       </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>BYG201-460-KAF-326</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Error: Value cannot be null. (Parameter 'input')</t>
+          <t>326</t>
         </is>
       </c>
       <c r="Q46" t="n">
@@ -6802,7 +6977,7 @@
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>Mangler gyldig merke/sekvens; Merke/sekvens avviker fra representant; Mangler rominfo</t>
+          <t>Mangler rominfo</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
@@ -6877,9 +7052,14 @@
           <t>True</t>
         </is>
       </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>BYG201-460-KAF-326</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Error: Value cannot be null. (Parameter 'input')</t>
+          <t>326</t>
         </is>
       </c>
       <c r="Q47" t="n">
@@ -6902,7 +7082,7 @@
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>Mangler gyldig merke/sekvens; Merke/sekvens avviker fra representant; Mangler rominfo</t>
+          <t>Mangler rominfo</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
@@ -6977,9 +7157,14 @@
           <t>True</t>
         </is>
       </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>BYG201-460-KAF-326</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Error: Value cannot be null. (Parameter 'input')</t>
+          <t>326</t>
         </is>
       </c>
       <c r="Q48" t="n">
@@ -7002,7 +7187,7 @@
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>Mangler gyldig merke/sekvens; Merke/sekvens avviker fra representant; Mangler rominfo</t>
+          <t>Mangler rominfo</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
@@ -7077,9 +7262,14 @@
           <t>True</t>
         </is>
       </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>BYG201-460-KAF-326</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Error: Value cannot be null. (Parameter 'input')</t>
+          <t>326</t>
         </is>
       </c>
       <c r="Q49" t="n">
@@ -7102,7 +7292,7 @@
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>Mangler gyldig merke/sekvens; Merke/sekvens avviker fra representant; Mangler rominfo</t>
+          <t>Mangler rominfo</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
@@ -7179,12 +7369,12 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>BYG202-460-KAF-319</t>
+          <t>BYG202-460-KAF-230</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>319</t>
+          <t>230</t>
         </is>
       </c>
       <c r="Q50" t="n">
@@ -7217,7 +7407,7 @@
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>Merke/sekvens avviker fra representant</t>
+          <t>Kontrollerte felt samsvarer i snapshot</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
@@ -7294,12 +7484,12 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>BYG202-460-KAF-229</t>
+          <t>BYG202-460-KAF-230</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>230</t>
         </is>
       </c>
       <c r="Q51" t="n">
@@ -7332,7 +7522,7 @@
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>Merke/sekvens avviker fra representant</t>
+          <t>Kontrollerte felt samsvarer i snapshot</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
@@ -7524,12 +7714,12 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>BYG202-460-KAF-231</t>
+          <t>BYG202-460-KAF-230</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>230</t>
         </is>
       </c>
       <c r="Q53" t="n">
@@ -7562,7 +7752,7 @@
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>Merke/sekvens avviker fra representant</t>
+          <t>Kontrollerte felt samsvarer i snapshot</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
@@ -7639,12 +7829,12 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>BYG202-460-KAF-232</t>
+          <t>BYG202-460-KAF-230</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>230</t>
         </is>
       </c>
       <c r="Q54" t="n">
@@ -7677,7 +7867,7 @@
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>Merke/sekvens avviker fra representant</t>
+          <t>Kontrollerte felt samsvarer i snapshot</t>
         </is>
       </c>
       <c r="X54" t="inlineStr">
@@ -7754,12 +7944,12 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>BYG202-460-KAF-242</t>
+          <t>BYG202-460-KAF-230</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>230</t>
         </is>
       </c>
       <c r="Q55" t="n">
@@ -7792,7 +7982,7 @@
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>Merke/sekvens avviker fra representant</t>
+          <t>Kontrollerte felt samsvarer i snapshot</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
@@ -7869,12 +8059,12 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>BYG201-460-KAF-060</t>
+          <t>BYG201-460-KAF-062</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>060</t>
+          <t>062</t>
         </is>
       </c>
       <c r="Q56" t="n">
@@ -7907,7 +8097,7 @@
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>Merke/sekvens avviker fra representant</t>
+          <t>Kontrollerte felt samsvarer i snapshot</t>
         </is>
       </c>
       <c r="X56" t="inlineStr">
@@ -8099,12 +8289,12 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>BYG201-460-KAF-280</t>
+          <t>BYG201-460-KAF-063</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>063</t>
         </is>
       </c>
       <c r="Q58" t="n">
@@ -8137,7 +8327,7 @@
       </c>
       <c r="W58" t="inlineStr">
         <is>
-          <t>Merke/sekvens avviker fra representant</t>
+          <t>Kontrollerte felt samsvarer i snapshot</t>
         </is>
       </c>
       <c r="X58" t="inlineStr">
@@ -8329,12 +8519,12 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>BYG201-460-KAF-011</t>
+          <t>BYG201-460-KAF-072</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>011</t>
+          <t>072</t>
         </is>
       </c>
       <c r="Q60" t="n">
@@ -8367,7 +8557,7 @@
       </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t>Merke/sekvens avviker fra representant</t>
+          <t>Kontrollerte felt samsvarer i snapshot</t>
         </is>
       </c>
       <c r="X60" t="inlineStr">
@@ -8559,12 +8749,12 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>P14-460-KAF-007</t>
+          <t>P14-460-KAF-008</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>007</t>
+          <t>008</t>
         </is>
       </c>
       <c r="Q62" t="n">
@@ -8592,7 +8782,7 @@
       </c>
       <c r="W62" t="inlineStr">
         <is>
-          <t>Merke/sekvens avviker fra representant</t>
+          <t>Kontrollerte felt samsvarer i snapshot</t>
         </is>
       </c>
       <c r="X62" t="inlineStr">
@@ -8779,12 +8969,12 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>P14-460-KAF-009</t>
+          <t>P14-460-KAF-008</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>009</t>
+          <t>008</t>
         </is>
       </c>
       <c r="Q64" t="n">
@@ -8812,7 +9002,7 @@
       </c>
       <c r="W64" t="inlineStr">
         <is>
-          <t>Merke/sekvens avviker fra representant</t>
+          <t>Kontrollerte felt samsvarer i snapshot</t>
         </is>
       </c>
       <c r="X64" t="inlineStr">
@@ -8889,12 +9079,12 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>BYG202-460-KAF-409</t>
+          <t>BYG202-460-KAF-249</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>409</t>
+          <t>249</t>
         </is>
       </c>
       <c r="Q65" t="n">
@@ -8922,7 +9112,7 @@
       </c>
       <c r="W65" t="inlineStr">
         <is>
-          <t>Merke/sekvens avviker fra representant</t>
+          <t>Kontrollerte felt samsvarer i snapshot</t>
         </is>
       </c>
       <c r="X65" t="inlineStr">
@@ -9109,12 +9299,12 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>BYG202-460-KAF-236</t>
+          <t>BYG202-460-KAF-261</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>261</t>
         </is>
       </c>
       <c r="Q67" t="n">
@@ -9147,7 +9337,7 @@
       </c>
       <c r="W67" t="inlineStr">
         <is>
-          <t>Merke/sekvens avviker fra representant</t>
+          <t>Kontrollerte felt samsvarer i snapshot</t>
         </is>
       </c>
       <c r="X67" t="inlineStr">
@@ -9224,12 +9414,12 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>BYG202-460-KAF-260</t>
+          <t>BYG202-460-KAF-261</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>261</t>
         </is>
       </c>
       <c r="Q68" t="n">
@@ -9262,7 +9452,7 @@
       </c>
       <c r="W68" t="inlineStr">
         <is>
-          <t>Merke/sekvens avviker fra representant</t>
+          <t>Kontrollerte felt samsvarer i snapshot</t>
         </is>
       </c>
       <c r="X68" t="inlineStr">
@@ -9454,12 +9644,12 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>BYG202-460-KAF-443</t>
+          <t>BYG202-460-KAF-262</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>443</t>
+          <t>262</t>
         </is>
       </c>
       <c r="Q70" t="n">
@@ -9492,7 +9682,7 @@
       </c>
       <c r="W70" t="inlineStr">
         <is>
-          <t>Merke/sekvens avviker fra representant</t>
+          <t>Kontrollerte felt samsvarer i snapshot</t>
         </is>
       </c>
       <c r="X70" t="inlineStr">
@@ -9569,12 +9759,12 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>BYG202-460-KAF-444</t>
+          <t>BYG202-460-KAF-262</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>444</t>
+          <t>262</t>
         </is>
       </c>
       <c r="Q71" t="n">
@@ -9607,7 +9797,7 @@
       </c>
       <c r="W71" t="inlineStr">
         <is>
-          <t>Merke/sekvens avviker fra representant; Rominfo avviker – avklar</t>
+          <t>Rominfo avviker – avklar</t>
         </is>
       </c>
       <c r="X71" t="inlineStr">
@@ -9684,12 +9874,12 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>BYG202-460-KAF-445</t>
+          <t>BYG202-460-KAF-262</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>445</t>
+          <t>262</t>
         </is>
       </c>
       <c r="Q72" t="n">
@@ -9722,7 +9912,7 @@
       </c>
       <c r="W72" t="inlineStr">
         <is>
-          <t>Merke/sekvens avviker fra representant; Rominfo avviker – avklar</t>
+          <t>Rominfo avviker – avklar</t>
         </is>
       </c>
       <c r="X72" t="inlineStr">
@@ -9914,12 +10104,12 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>BYG203-460-KAF-062</t>
+          <t>BYG203-460-KAF-068</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>062</t>
+          <t>068</t>
         </is>
       </c>
       <c r="Q74" t="n">
@@ -9952,7 +10142,7 @@
       </c>
       <c r="W74" t="inlineStr">
         <is>
-          <t>Merke/sekvens avviker fra representant</t>
+          <t>Kontrollerte felt samsvarer i snapshot</t>
         </is>
       </c>
       <c r="X74" t="inlineStr">
@@ -10095,7 +10285,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z54"/>
+  <dimension ref="A1:Z18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -10113,14 +10303,14 @@
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="20" customWidth="1" min="15" max="15"/>
-    <col width="50" customWidth="1" min="16" max="16"/>
+    <col width="15" customWidth="1" min="16" max="16"/>
     <col width="14" customWidth="1" min="17" max="17"/>
     <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="25" customWidth="1" min="19" max="19"/>
+    <col width="22" customWidth="1" min="19" max="19"/>
     <col width="20" customWidth="1" min="20" max="20"/>
-    <col width="50" customWidth="1" min="21" max="21"/>
+    <col width="21" customWidth="1" min="21" max="21"/>
     <col width="23" customWidth="1" min="22" max="22"/>
-    <col width="55" customWidth="1" min="23" max="23"/>
+    <col width="26" customWidth="1" min="23" max="23"/>
     <col width="54" customWidth="1" min="24" max="24"/>
     <col width="47" customWidth="1" min="25" max="25"/>
     <col width="14" customWidth="1" min="26" max="26"/>
@@ -10261,7 +10451,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BAS-10227355</t>
+          <t>BAS-10980188</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -10271,22 +10461,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>10227355</t>
+          <t>10980188</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>9906846</t>
+          <t>16706421</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>18fa763f-02ee-4055-a811-c0110f396833-00972a9e</t>
+          <t>110a7c5a-15e3-4ec7-bae8-2091ab9343fc-00feeb75</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>826f95e9-696b-4e03-8d42-646adf32ede0-009c0e9b</t>
+          <t>40a1d429-7fcb-4f0d-8e19-7971adc990b5-00a78b5c</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -10306,10 +10496,10 @@
         <v>60</v>
       </c>
       <c r="K2" t="n">
-        <v>808093</v>
+        <v>808765</v>
       </c>
       <c r="L2" t="n">
-        <v>808093</v>
+        <v>808765</v>
       </c>
       <c r="M2" t="n">
         <v>15501</v>
@@ -10321,45 +10511,45 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>BYG203-460-KAF-069</t>
+          <t>BYG201-460-KAF-153</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>069</t>
+          <t>153</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>495</v>
+        <v>2607</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>L4U2.05</t>
+          <t>L3S.08</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>Søppelrom og Støvsuger</t>
+          <t>Parkering gul maskin</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>BYG203-460-KAF-072</t>
+          <t>BYG201-460-KAF-153</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>072</t>
+          <t>153</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>L4U2.05</t>
+          <t>L3S.07</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Merke/sekvens avviker fra representant</t>
+          <t>Rominfo avviker – avklar</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -10391,12 +10581,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>16706421</t>
+          <t>17678343</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>110a7c5a-15e3-4ec7-bae8-2091ab9343fc-00feeb75</t>
+          <t>bcb00db8-e87a-41b9-8e49-76b1504b40e2-010dc007</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -10421,10 +10611,10 @@
         <v>60</v>
       </c>
       <c r="K3" t="n">
-        <v>808765</v>
+        <v>808778</v>
       </c>
       <c r="L3" t="n">
-        <v>808765</v>
+        <v>808778</v>
       </c>
       <c r="M3" t="n">
         <v>15501</v>
@@ -10436,12 +10626,12 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>BYG201-460-KAF-312</t>
+          <t>BYG201-460-KAF-153</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>153</t>
         </is>
       </c>
       <c r="Q3" t="n">
@@ -10474,7 +10664,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Merke/sekvens avviker fra representant; Rominfo avviker – avklar</t>
+          <t>Rominfo avviker – avklar</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -10506,12 +10696,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>17678343</t>
+          <t>8569079</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>bcb00db8-e87a-41b9-8e49-76b1504b40e2-010dc007</t>
+          <t>6e4008f6-a921-4b71-9bb1-122ecf38f100-0082c0f7</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -10536,10 +10726,10 @@
         <v>60</v>
       </c>
       <c r="K4" t="n">
-        <v>808778</v>
+        <v>807961</v>
       </c>
       <c r="L4" t="n">
-        <v>808778</v>
+        <v>807961</v>
       </c>
       <c r="M4" t="n">
         <v>15501</v>
@@ -10551,12 +10741,12 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>BYG201-460-KAF-314</t>
+          <t>BYG201-460-KAF-153</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>153</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -10589,7 +10779,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Merke/sekvens avviker fra representant; Rominfo avviker – avklar</t>
+          <t>Rominfo avviker – avklar</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -10606,7 +10796,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BAS-10980188</t>
+          <t>BAS-12264136</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -10616,22 +10806,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>10980188</t>
+          <t>12264136</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8569079</t>
+          <t>14211731</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>6e4008f6-a921-4b71-9bb1-122ecf38f100-0082c0f7</t>
+          <t>78c9b82b-62d2-4e8f-a385-7137eec5e4ef-00d8da93</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>40a1d429-7fcb-4f0d-8e19-7971adc990b5-00a78b5c</t>
+          <t>a602c242-146b-47cf-93d1-b8052ca793fb-00bb22c8</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -10651,10 +10841,10 @@
         <v>60</v>
       </c>
       <c r="K5" t="n">
-        <v>807961</v>
+        <v>808499</v>
       </c>
       <c r="L5" t="n">
-        <v>807961</v>
+        <v>808499</v>
       </c>
       <c r="M5" t="n">
         <v>15501</v>
@@ -10666,45 +10856,35 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>BYG201-460-KAF-095</t>
+          <t>P14-460-KAF-041</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>095</t>
+          <t>041</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>2607</v>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>L3S.08</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>Parkering gul maskin</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>BYG201-460-KAF-153</t>
+          <t>P14-460-KAF-041</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>041</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>L3S.07</t>
+          <t>L4S.28</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Merke/sekvens avviker fra representant; Rominfo avviker – avklar</t>
+          <t>Mangler rominfo</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -10721,7 +10901,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BAS-11208647</t>
+          <t>BAS-12265369</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -10731,27 +10911,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>11208647</t>
+          <t>12265369</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>11208778</t>
+          <t>12724055</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>5e051539-a3af-4622-8d97-fe023a01d872-00ab084a</t>
+          <t>ed230345-c369-4edd-aefb-f3b39f158476-00c22757</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>5e051539-a3af-4622-8d97-fe023a01d872-00ab07c7</t>
+          <t>a602c242-146b-47cf-93d1-b8052ca793fb-00bb2799</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Kabelstige 300 mm x 60 mm</t>
+          <t>Kabelstige 600 mm x 60 mm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -10760,19 +10940,19 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="J6" t="n">
         <v>60</v>
       </c>
       <c r="K6" t="n">
-        <v>808206</v>
+        <v>809091</v>
       </c>
       <c r="L6" t="n">
-        <v>808206</v>
+        <v>809091</v>
       </c>
       <c r="M6" t="n">
-        <v>15501</v>
+        <v>15499</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -10781,45 +10961,35 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>BYG201-460-KAF-165</t>
+          <t>P14-460-KAF-042</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>042</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>2249</v>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>E2S.01</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>Spor P6-P7 nord</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>BYG201-460-KAF-164</t>
+          <t>P14-460-KAF-042</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>042</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>E2S.01</t>
+          <t>L4S.28</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Merke/sekvens avviker fra representant</t>
+          <t>Mangler rominfo</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -10836,7 +11006,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BAS-11226330</t>
+          <t>BAS-13562661</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -10846,27 +11016,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>11226330</t>
+          <t>13562661</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>11226215</t>
+          <t>15673873</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>94efd9e4-d480-4349-832d-c2ef7cc26dde-00ab4c67</t>
+          <t>231f187a-cecb-4eab-b1a8-083ce21ac82d-00ef2a11</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>94efd9e4-d480-4349-832d-c2ef7cc26dde-00ab4cda</t>
+          <t>9d97dabc-13c0-4b7a-84de-8f37b4b68345-00ceef71</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Kabelstige 300 mm x 60 mm</t>
+          <t>Kabelstige 600 mm x 60 mm</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -10875,19 +11045,19 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="J7" t="n">
         <v>60</v>
       </c>
       <c r="K7" t="n">
-        <v>808212</v>
+        <v>809155</v>
       </c>
       <c r="L7" t="n">
-        <v>808212</v>
+        <v>809155</v>
       </c>
       <c r="M7" t="n">
-        <v>15501</v>
+        <v>15499</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -10896,45 +11066,45 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>BYG201-460-KAF-171</t>
+          <t>BYG202-460-KAF-384</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>384</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>2250</v>
+        <v>564</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>E8S.01</t>
+          <t>M3G2.03</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>Nord</t>
+          <t>Lager, innerst</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>BYG201-460-KAF-172</t>
+          <t>BYG202-460-KAF-384</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>384</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>E8S.01</t>
+          <t>M3G2.03</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Merke/sekvens avviker fra representant</t>
+          <t>Rominfo avviker – avklar</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -10951,7 +11121,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BAS-11226330</t>
+          <t>BAS-13562661</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -10961,27 +11131,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>11226330</t>
+          <t>13562661</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>11226448</t>
+          <t>8013071</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>94efd9e4-d480-4349-832d-c2ef7cc26dde-00ab4d50</t>
+          <t>0a8275bd-5c9b-4e27-bc36-a7081356468c-007a450f</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>94efd9e4-d480-4349-832d-c2ef7cc26dde-00ab4cda</t>
+          <t>9d97dabc-13c0-4b7a-84de-8f37b4b68345-00ceef71</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Kabelstige 300 mm x 60 mm</t>
+          <t>Kabelstige 600 mm x 60 mm</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -10990,19 +11160,19 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="J8" t="n">
         <v>60</v>
       </c>
       <c r="K8" t="n">
-        <v>808214</v>
+        <v>808982</v>
       </c>
       <c r="L8" t="n">
-        <v>808214</v>
+        <v>808982</v>
       </c>
       <c r="M8" t="n">
-        <v>15501</v>
+        <v>15499</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -11011,45 +11181,45 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>BYG201-460-KAF-173</t>
+          <t>BYG202-460-KAF-384</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>384</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>2250</v>
+        <v>564</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>E8S.01</t>
+          <t>M3G2.03</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>Nord</t>
+          <t>Lager, innerst</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>BYG201-460-KAF-172</t>
+          <t>BYG202-460-KAF-384</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>384</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>E8S.01</t>
+          <t>M3G2.03</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Merke/sekvens avviker fra representant</t>
+          <t>Rominfo avviker – avklar</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -11066,7 +11236,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BAS-11226629</t>
+          <t>BAS-300-C3S02</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -11076,27 +11246,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>11226629</t>
+          <t>12351764</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>14195528</t>
+          <t>12351767</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>e9fdb864-4ab5-4fe0-a4b9-b1d4c455e9e7-00d89b48</t>
+          <t>5f883497-5a39-4b7c-b120-6b279b0b6c8e-00bb3300</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>94efd9e4-d480-4349-832d-c2ef7cc26dde-00ab4e05</t>
+          <t>5f883497-5a39-4b7c-b120-6b279b0b6c8e-00bb31fa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Kabelstige 200 mm x 60 mm</t>
+          <t>Kabelstige 300 mm x 60 mm</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -11105,19 +11275,19 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="J9" t="n">
         <v>60</v>
       </c>
       <c r="K9" t="n">
-        <v>808487</v>
+        <v>808279</v>
       </c>
       <c r="L9" t="n">
-        <v>808487</v>
+        <v>808279</v>
       </c>
       <c r="M9" t="n">
-        <v>15503</v>
+        <v>15501</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -11126,45 +11296,35 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>BYG201-460-KAF-231</t>
+          <t>BYG201-460-KAF-011</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>011</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>2250</v>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>E8S.01</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>Nord</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>BYG201-460-KAF-174</t>
+          <t>BYG201-460-KAF-011</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>011</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>E8S.01</t>
+          <t>C3S.02</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Merke/sekvens avviker fra representant</t>
+          <t>Mangler rominfo</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -11181,7 +11341,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BAS-11226629</t>
+          <t>BAS-300-C3S02</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -11191,27 +11351,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>11226629</t>
+          <t>12351764</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>14195632</t>
+          <t>12351769</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>e9fdb864-4ab5-4fe0-a4b9-b1d4c455e9e7-00d89bb0</t>
+          <t>5f883497-5a39-4b7c-b120-6b279b0b6c8e-00bb338a</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>94efd9e4-d480-4349-832d-c2ef7cc26dde-00ab4e05</t>
+          <t>5f883497-5a39-4b7c-b120-6b279b0b6c8e-00bb31fa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Kabelstige 200 mm x 60 mm</t>
+          <t>Kabelstige 300 mm x 60 mm</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -11220,19 +11380,19 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="J10" t="n">
         <v>60</v>
       </c>
       <c r="K10" t="n">
-        <v>808488</v>
+        <v>808280</v>
       </c>
       <c r="L10" t="n">
-        <v>808488</v>
+        <v>808280</v>
       </c>
       <c r="M10" t="n">
-        <v>15503</v>
+        <v>15501</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -11241,45 +11401,35 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>BYG201-460-KAF-232</t>
+          <t>BYG201-460-KAF-011</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>011</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>2250</v>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>E8S.01</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>Nord</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>BYG201-460-KAF-174</t>
+          <t>BYG201-460-KAF-011</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>011</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>E8S.01</t>
+          <t>C3S.02</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Merke/sekvens avviker fra representant</t>
+          <t>Mangler rominfo</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -11296,7 +11446,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BAS-11226629</t>
+          <t>BAS-300-C3S02</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -11306,27 +11456,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>11226629</t>
+          <t>12351764</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>15395207</t>
+          <t>12351771</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>c3968702-07ae-4936-b7a9-15eb4d6707d7-00eae987</t>
+          <t>5f883497-5a39-4b7c-b120-6b279b0b6c8e-00bb3441</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>94efd9e4-d480-4349-832d-c2ef7cc26dde-00ab4e05</t>
+          <t>5f883497-5a39-4b7c-b120-6b279b0b6c8e-00bb31fa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Kabelstige 200 mm x 60 mm</t>
+          <t>Kabelstige 300 mm x 60 mm</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -11335,19 +11485,19 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="J11" t="n">
         <v>60</v>
       </c>
       <c r="K11" t="n">
-        <v>808577</v>
+        <v>808281</v>
       </c>
       <c r="L11" t="n">
-        <v>808577</v>
+        <v>808281</v>
       </c>
       <c r="M11" t="n">
-        <v>15503</v>
+        <v>15501</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -11356,45 +11506,35 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>BYG201-460-KAF-278</t>
+          <t>BYG201-460-KAF-011</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>011</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>2250</v>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>E8S.01</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>Nord</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>BYG201-460-KAF-174</t>
+          <t>BYG201-460-KAF-011</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>011</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>E8S.01</t>
+          <t>C3S.02</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>Merke/sekvens avviker fra representant</t>
+          <t>Mangler rominfo</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -11411,7 +11551,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BAS-12264136</t>
+          <t>BAS-300-C3S02</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -11421,22 +11561,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>12264136</t>
+          <t>12351764</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>14211731</t>
+          <t>12351773</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>78c9b82b-62d2-4e8f-a385-7137eec5e4ef-00d8da93</t>
+          <t>5f883497-5a39-4b7c-b120-6b279b0b6c8e-00bb3514</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>a602c242-146b-47cf-93d1-b8052ca793fb-00bb22c8</t>
+          <t>5f883497-5a39-4b7c-b120-6b279b0b6c8e-00bb31fa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -11456,10 +11596,10 @@
         <v>60</v>
       </c>
       <c r="K12" t="n">
-        <v>808499</v>
+        <v>808282</v>
       </c>
       <c r="L12" t="n">
-        <v>808499</v>
+        <v>808282</v>
       </c>
       <c r="M12" t="n">
         <v>15501</v>
@@ -11469,9 +11609,14 @@
           <t>True</t>
         </is>
       </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>BYG201-460-KAF-011</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Error: Value cannot be null. (Parameter 'input')</t>
+          <t>011</t>
         </is>
       </c>
       <c r="Q12" t="n">
@@ -11479,22 +11624,22 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>P14-460-KAF-041</t>
+          <t>BYG201-460-KAF-011</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>041</t>
+          <t>011</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>L4S.28</t>
+          <t>C3S.02</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Mangler gyldig merke/sekvens; Merke/sekvens avviker fra representant; Mangler rominfo</t>
+          <t>Mangler rominfo</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -11511,7 +11656,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BAS-12264596</t>
+          <t>BAS-600-C3S02</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -11521,27 +11666,27 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>12264596</t>
+          <t>12262924</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>11835782</t>
+          <t>12351754</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>43994072-83b2-4b9c-82ab-d4f3df0fefa7-00b49986</t>
+          <t>5f883497-5a39-4b7c-b120-6b279b0b6c8e-00bb2d2b</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>a602c242-146b-47cf-93d1-b8052ca793fb-00bb2494</t>
+          <t>3de28406-8391-46ef-a35b-32becf36f03e-00bb1e0c</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Kabelstige 300 mm x 60 mm</t>
+          <t>Kabelstige 600 mm x 60 mm</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -11550,19 +11695,19 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="J13" t="n">
         <v>60</v>
       </c>
       <c r="K13" t="n">
-        <v>808223</v>
+        <v>809079</v>
       </c>
       <c r="L13" t="n">
-        <v>808223</v>
+        <v>809079</v>
       </c>
       <c r="M13" t="n">
-        <v>15501</v>
+        <v>15499</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -11571,40 +11716,35 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>P14-460-KAF-022</t>
+          <t>BYG201-460-KAF-326</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>022</t>
+          <t>326</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>4209</v>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>L4S.28</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>P14-460-KAF-028</t>
+          <t>BYG201-460-KAF-326</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>028</t>
+          <t>326</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>L4S.28</t>
+          <t>C3S.02</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Merke/sekvens avviker fra representant</t>
+          <t>Mangler rominfo</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -11621,7 +11761,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BAS-12264596</t>
+          <t>BAS-600-C3S02</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -11631,27 +11771,27 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>12264596</t>
+          <t>12262924</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>12262584</t>
+          <t>12351756</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>46fc8cd2-1877-448f-9053-b52d2c310730-00bb142f</t>
+          <t>5f883497-5a39-4b7c-b120-6b279b0b6c8e-00bb2df1</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>a602c242-146b-47cf-93d1-b8052ca793fb-00bb2494</t>
+          <t>3de28406-8391-46ef-a35b-32becf36f03e-00bb1e0c</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Kabelstige 300 mm x 60 mm</t>
+          <t>Kabelstige 600 mm x 60 mm</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -11660,19 +11800,19 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="J14" t="n">
         <v>60</v>
       </c>
       <c r="K14" t="n">
-        <v>808264</v>
+        <v>809080</v>
       </c>
       <c r="L14" t="n">
-        <v>808264</v>
+        <v>809080</v>
       </c>
       <c r="M14" t="n">
-        <v>15501</v>
+        <v>15499</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -11681,40 +11821,35 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>P14-460-KAF-024</t>
+          <t>BYG201-460-KAF-326</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>024</t>
+          <t>326</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>4209</v>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>L4S.28</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>P14-460-KAF-028</t>
+          <t>BYG201-460-KAF-326</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>028</t>
+          <t>326</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>L4S.28</t>
+          <t>C3S.02</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>Merke/sekvens avviker fra representant</t>
+          <t>Mangler rominfo</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -11731,7 +11866,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BAS-12264596</t>
+          <t>BAS-600-C3S02</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -11741,27 +11876,27 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>12264596</t>
+          <t>12262924</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>12262585</t>
+          <t>12351758</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>46fc8cd2-1877-448f-9053-b52d2c310730-00bb146c</t>
+          <t>5f883497-5a39-4b7c-b120-6b279b0b6c8e-00bb2f89</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>a602c242-146b-47cf-93d1-b8052ca793fb-00bb2494</t>
+          <t>3de28406-8391-46ef-a35b-32becf36f03e-00bb1e0c</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Kabelstige 300 mm x 60 mm</t>
+          <t>Kabelstige 600 mm x 60 mm</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -11770,19 +11905,19 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="J15" t="n">
         <v>60</v>
       </c>
       <c r="K15" t="n">
-        <v>808265</v>
+        <v>809081</v>
       </c>
       <c r="L15" t="n">
-        <v>808265</v>
+        <v>809081</v>
       </c>
       <c r="M15" t="n">
-        <v>15501</v>
+        <v>15499</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -11791,40 +11926,35 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>P14-460-KAF-025</t>
+          <t>BYG201-460-KAF-326</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>326</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>4209</v>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>L4S.28</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>P14-460-KAF-028</t>
+          <t>BYG201-460-KAF-326</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>028</t>
+          <t>326</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>L4S.28</t>
+          <t>C3S.02</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>Merke/sekvens avviker fra representant</t>
+          <t>Mangler rominfo</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -11841,7 +11971,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BAS-12265369</t>
+          <t>BAS-600-C3S02</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -11851,22 +11981,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>12265369</t>
+          <t>12262924</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>12265222</t>
+          <t>12351760</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>a602c242-146b-47cf-93d1-b8052ca793fb-00bb2706</t>
+          <t>5f883497-5a39-4b7c-b120-6b279b0b6c8e-00bb3013</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>a602c242-146b-47cf-93d1-b8052ca793fb-00bb2799</t>
+          <t>3de28406-8391-46ef-a35b-32becf36f03e-00bb1e0c</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -11886,10 +12016,10 @@
         <v>60</v>
       </c>
       <c r="K16" t="n">
-        <v>809077</v>
+        <v>809082</v>
       </c>
       <c r="L16" t="n">
-        <v>809077</v>
+        <v>809082</v>
       </c>
       <c r="M16" t="n">
         <v>15499</v>
@@ -11901,40 +12031,35 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>P14-460-KAF-029</t>
+          <t>BYG201-460-KAF-326</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>029</t>
+          <t>326</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>4209</v>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>L4S.28</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>P14-460-KAF-042</t>
+          <t>BYG201-460-KAF-326</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>042</t>
+          <t>326</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>L4S.28</t>
+          <t>C3S.02</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Merke/sekvens avviker fra representant</t>
+          <t>Mangler rominfo</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -11951,7 +12076,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BAS-12265369</t>
+          <t>BAS-9356413</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -11961,27 +12086,27 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>12265369</t>
+          <t>9356413</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>12724055</t>
+          <t>17483581</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ed230345-c369-4edd-aefb-f3b39f158476-00c22757</t>
+          <t>4ad1b7f0-f3ce-4589-831d-0bf2df01d6ac-010ac73d</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>a602c242-146b-47cf-93d1-b8052ca793fb-00bb2799</t>
+          <t>55ec083c-7f8f-44f9-940c-a3375ca937f7-008ec47d</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Kabelstige 600 mm x 60 mm</t>
+          <t>Kabelstige 800 mm x 60 mm</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -11990,51 +12115,66 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="J17" t="n">
         <v>60</v>
       </c>
       <c r="K17" t="n">
-        <v>809091</v>
+        <v>808775</v>
       </c>
       <c r="L17" t="n">
-        <v>809091</v>
+        <v>808775</v>
       </c>
       <c r="M17" t="n">
-        <v>15499</v>
+        <v>16281</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>BYG202-460-KAF-262</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Error: Value cannot be null. (Parameter 'input')</t>
+          <t>262</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3850</v>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>L3S.02</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>Innkjøring</t>
+        </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>P14-460-KAF-042</t>
+          <t>BYG202-460-KAF-262</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>042</t>
+          <t>262</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>L4S.28</t>
+          <t>M3G2.03</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Mangler gyldig merke/sekvens; Merke/sekvens avviker fra representant; Mangler rominfo</t>
+          <t>Rominfo avviker – avklar</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -12051,7 +12191,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BAS-13562661</t>
+          <t>BAS-9356413</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -12061,27 +12201,27 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>13562661</t>
+          <t>9356413</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>15673873</t>
+          <t>17483715</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>231f187a-cecb-4eab-b1a8-083ce21ac82d-00ef2a11</t>
+          <t>4ad1b7f0-f3ce-4589-831d-0bf2df01d6ac-010ac7c3</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>9d97dabc-13c0-4b7a-84de-8f37b4b68345-00ceef71</t>
+          <t>55ec083c-7f8f-44f9-940c-a3375ca937f7-008ec47d</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Kabelstige 600 mm x 60 mm</t>
+          <t>Kabelstige 800 mm x 60 mm</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -12090,19 +12230,19 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="J18" t="n">
         <v>60</v>
       </c>
       <c r="K18" t="n">
-        <v>809155</v>
+        <v>808776</v>
       </c>
       <c r="L18" t="n">
-        <v>809155</v>
+        <v>808776</v>
       </c>
       <c r="M18" t="n">
-        <v>15499</v>
+        <v>16281</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -12111,45 +12251,45 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>BYG202-460-KAF-415</t>
+          <t>BYG202-460-KAF-262</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>415</t>
+          <t>262</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>564</v>
+        <v>3850</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
+          <t>L3S.02</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>Innkjøring</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>BYG202-460-KAF-262</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
           <t>M3G2.03</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>Lager, innerst</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>BYG202-460-KAF-384</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>384</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>M3G2.03</t>
-        </is>
-      </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Merke/sekvens avviker fra representant; Rominfo avviker – avklar</t>
+          <t>Rominfo avviker – avklar</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -12158,3891 +12298,6 @@
         </is>
       </c>
       <c r="Y18" t="inlineStr">
-        <is>
-          <t>5e8f81e4-fcff-4378-8a08-70d893e9ab6c-0110f8e2</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>BAS-13562661</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Segment</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>13562661</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>8013071</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>0a8275bd-5c9b-4e27-bc36-a7081356468c-007a450f</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>9d97dabc-13c0-4b7a-84de-8f37b4b68345-00ceef71</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Kabelstige 600 mm x 60 mm</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>600</v>
-      </c>
-      <c r="J19" t="n">
-        <v>60</v>
-      </c>
-      <c r="K19" t="n">
-        <v>808982</v>
-      </c>
-      <c r="L19" t="n">
-        <v>808982</v>
-      </c>
-      <c r="M19" t="n">
-        <v>15499</v>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>BYG202-460-KAF-240</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
-      </c>
-      <c r="Q19" t="n">
-        <v>564</v>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>M3G2.03</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>Lager, innerst</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>BYG202-460-KAF-384</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>384</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>M3G2.03</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>Merke/sekvens avviker fra representant; Rominfo avviker – avklar</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>Autodesk Docs://Fornebubanen/U_F_BAS_FBU_RIE_XXX.rvt</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>5e8f81e4-fcff-4378-8a08-70d893e9ab6c-0110f8e2</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>BAS-16176184</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Segment</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>16176184</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>13296838</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>def0d1c3-fe7f-424b-b7d6-c03628d91521-00cae4c6</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>4ac2ac7e-3dfc-4f0b-a769-9b25f15c5586-00f6d438</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Kabelstige 200 mm x 60 mm</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>200</v>
-      </c>
-      <c r="J20" t="n">
-        <v>60</v>
-      </c>
-      <c r="K20" t="n">
-        <v>808399</v>
-      </c>
-      <c r="L20" t="n">
-        <v>808399</v>
-      </c>
-      <c r="M20" t="n">
-        <v>15503</v>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>BYG201-460-KAF-222</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
-      <c r="Q20" t="n">
-        <v>2796</v>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>E3S.01</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>Spor P8-P9 nord</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>Error: Value cannot be null. (Parameter 'input')</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>Representant mangler gyldig merkekilde; Rominfo avviker – avklar</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>Autodesk Docs://Fornebubanen/U_F_BAS_FBU_RIE_XXX.rvt</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>5e8f81e4-fcff-4378-8a08-70d893e9ab6c-0110f8e2</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>BAS-16176184</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Segment</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>16176184</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>15676090</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>dfeffabe-7034-42c2-b802-ef68d67dc765-00ef32ba</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>4ac2ac7e-3dfc-4f0b-a769-9b25f15c5586-00f6d438</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Kabelstige 200 mm x 60 mm</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>200</v>
-      </c>
-      <c r="J21" t="n">
-        <v>60</v>
-      </c>
-      <c r="K21" t="n">
-        <v>808596</v>
-      </c>
-      <c r="L21" t="n">
-        <v>808596</v>
-      </c>
-      <c r="M21" t="n">
-        <v>15503</v>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>BYG201-460-KAF-289</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>289</t>
-        </is>
-      </c>
-      <c r="Q21" t="n">
-        <v>2796</v>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>E3S.01</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>Spor P8-P9 nord</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>Error: Value cannot be null. (Parameter 'input')</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>Representant mangler gyldig merkekilde; Rominfo avviker – avklar</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>Autodesk Docs://Fornebubanen/U_F_BAS_FBU_RIE_XXX.rvt</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>5e8f81e4-fcff-4378-8a08-70d893e9ab6c-0110f8e2</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>BAS-16176184</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Segment</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>16176184</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>15676316</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>dfeffabe-7034-42c2-b802-ef68d67dc765-00ef339c</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>4ac2ac7e-3dfc-4f0b-a769-9b25f15c5586-00f6d438</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Kabelstige 200 mm x 60 mm</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>200</v>
-      </c>
-      <c r="J22" t="n">
-        <v>60</v>
-      </c>
-      <c r="K22" t="n">
-        <v>808597</v>
-      </c>
-      <c r="L22" t="n">
-        <v>808597</v>
-      </c>
-      <c r="M22" t="n">
-        <v>15503</v>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>BYG201-460-KAF-290</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>290</t>
-        </is>
-      </c>
-      <c r="Q22" t="n">
-        <v>2796</v>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>E3S.01</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>Spor P8-P9 nord</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>Error: Value cannot be null. (Parameter 'input')</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>Representant mangler gyldig merkekilde; Rominfo avviker – avklar</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>Autodesk Docs://Fornebubanen/U_F_BAS_FBU_RIE_XXX.rvt</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>5e8f81e4-fcff-4378-8a08-70d893e9ab6c-0110f8e2</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>BAS-16176184</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Representant</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>16176184</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>16176184</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>4ac2ac7e-3dfc-4f0b-a769-9b25f15c5586-00f6d438</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>4ac2ac7e-3dfc-4f0b-a769-9b25f15c5586-00f6d438</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Kabelstige 200 mm x 60 mm</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>200</v>
-      </c>
-      <c r="J23" t="n">
-        <v>60</v>
-      </c>
-      <c r="K23" t="n">
-        <v>808629</v>
-      </c>
-      <c r="L23" t="n">
-        <v>808629</v>
-      </c>
-      <c r="M23" t="n">
-        <v>15503</v>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>Error: Value cannot be null. (Parameter 'input')</t>
-        </is>
-      </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>Error: Value cannot be null. (Parameter 'input')</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>Mangler gyldig merke/sekvens; Representant mangler gyldig merkekilde; Mangler rominfo</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>Autodesk Docs://Fornebubanen/U_F_BAS_FBU_RIE_XXX.rvt</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>5e8f81e4-fcff-4378-8a08-70d893e9ab6c-0110f8e2</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>BAS-16281954</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Segment</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>16281954</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>10227226</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>826f95e9-696b-4e03-8d42-646adf32ede0-009c0e1a</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>ce1980d2-d4d0-4b2f-a31c-bddcfa1b8223-00f87162</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Kabelstige 600 mm x 60 mm</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>600</v>
-      </c>
-      <c r="J24" t="n">
-        <v>60</v>
-      </c>
-      <c r="K24" t="n">
-        <v>809031</v>
-      </c>
-      <c r="L24" t="n">
-        <v>809031</v>
-      </c>
-      <c r="M24" t="n">
-        <v>15499</v>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>BYG203-460-KAF-071</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>071</t>
-        </is>
-      </c>
-      <c r="Q24" t="n">
-        <v>495</v>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>L4U2.05</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>Søppelrom og Støvsuger</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>BYG203-460-KAF-089</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>089</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>L4U2.05</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>Merke/sekvens avviker fra representant</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>Autodesk Docs://Fornebubanen/U_F_BAS_FBU_RIE_XXX.rvt</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>5e8f81e4-fcff-4378-8a08-70d893e9ab6c-0110f8e2</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>BAS-16281954</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Segment</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>16281954</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>13236302</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>cdc76089-6454-48ee-9be0-2c1dd0f4fd57-00c9f84e</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>ce1980d2-d4d0-4b2f-a31c-bddcfa1b8223-00f87162</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Kabelstige 600 mm x 60 mm</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>600</v>
-      </c>
-      <c r="J25" t="n">
-        <v>60</v>
-      </c>
-      <c r="K25" t="n">
-        <v>809102</v>
-      </c>
-      <c r="L25" t="n">
-        <v>809102</v>
-      </c>
-      <c r="M25" t="n">
-        <v>15499</v>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>BYG203-460-KAF-081</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>081</t>
-        </is>
-      </c>
-      <c r="Q25" t="n">
-        <v>495</v>
-      </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>L4U2.05</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>Søppelrom og Støvsuger</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>BYG203-460-KAF-089</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>089</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>L4U2.05</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>Merke/sekvens avviker fra representant</t>
-        </is>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>Autodesk Docs://Fornebubanen/U_F_BAS_FBU_RIE_XXX.rvt</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>5e8f81e4-fcff-4378-8a08-70d893e9ab6c-0110f8e2</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>BAS-16678174</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Segment</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>16678174</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>10997688</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>efde14f0-c9d7-44c2-b567-43df80ddc92b-00a7cfb8</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>cdd457a8-f0e4-4606-9746-4a8bf2720ab6-00fe7d1e</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Kabelstige 300 mm x 60 mm</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>300</v>
-      </c>
-      <c r="J26" t="n">
-        <v>60</v>
-      </c>
-      <c r="K26" t="n">
-        <v>808160</v>
-      </c>
-      <c r="L26" t="n">
-        <v>808160</v>
-      </c>
-      <c r="M26" t="n">
-        <v>15501</v>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>BYG201-460-KAF-158</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="Q26" t="n">
-        <v>567</v>
-      </c>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>L3S.06</t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>Parkering Gule Maskiner</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>BYG201-460-KAF-310</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>L3S.06</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>Merke/sekvens avviker fra representant</t>
-        </is>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>Autodesk Docs://Fornebubanen/U_F_BAS_FBU_RIE_XXX.rvt</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>5e8f81e4-fcff-4378-8a08-70d893e9ab6c-0110f8e2</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>BAS-16678174</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Segment</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>16678174</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>16678011</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>cdd457a8-f0e4-4606-9746-4a8bf2720ab6-00fe7c7b</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>cdd457a8-f0e4-4606-9746-4a8bf2720ab6-00fe7d1e</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Kabelstige 300 mm x 60 mm</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>300</v>
-      </c>
-      <c r="J27" t="n">
-        <v>60</v>
-      </c>
-      <c r="K27" t="n">
-        <v>808761</v>
-      </c>
-      <c r="L27" t="n">
-        <v>808761</v>
-      </c>
-      <c r="M27" t="n">
-        <v>15501</v>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>BYG201-460-KAF-309</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>309</t>
-        </is>
-      </c>
-      <c r="Q27" t="n">
-        <v>567</v>
-      </c>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>L3S.06</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>Parkering Gule Maskiner</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>BYG201-460-KAF-310</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>L3S.06</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>Merke/sekvens avviker fra representant</t>
-        </is>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>Autodesk Docs://Fornebubanen/U_F_BAS_FBU_RIE_XXX.rvt</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>5e8f81e4-fcff-4378-8a08-70d893e9ab6c-0110f8e2</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>BAS-16678174</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Segment</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>16678174</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>9708501</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>fddf30d1-0705-4174-a99f-9f701ad33496-009423d5</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>cdd457a8-f0e4-4606-9746-4a8bf2720ab6-00fe7d1e</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Kabelstige 300 mm x 60 mm</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
-        <v>300</v>
-      </c>
-      <c r="J28" t="n">
-        <v>60</v>
-      </c>
-      <c r="K28" t="n">
-        <v>808065</v>
-      </c>
-      <c r="L28" t="n">
-        <v>808065</v>
-      </c>
-      <c r="M28" t="n">
-        <v>15501</v>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>BYG201-460-KAF-129</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="Q28" t="n">
-        <v>567</v>
-      </c>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>L3S.06</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>Parkering Gule Maskiner</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>BYG201-460-KAF-310</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>L3S.06</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>Merke/sekvens avviker fra representant</t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>Autodesk Docs://Fornebubanen/U_F_BAS_FBU_RIE_XXX.rvt</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>5e8f81e4-fcff-4378-8a08-70d893e9ab6c-0110f8e2</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>BAS-300-C3S02</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Representant</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>12351764</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>12351764</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>5f883497-5a39-4b7c-b120-6b279b0b6c8e-00bb31fa</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>5f883497-5a39-4b7c-b120-6b279b0b6c8e-00bb31fa</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Kabelstige 300 mm x 60 mm</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="I29" t="n">
-        <v>300</v>
-      </c>
-      <c r="J29" t="n">
-        <v>60</v>
-      </c>
-      <c r="K29" t="n">
-        <v>808278</v>
-      </c>
-      <c r="L29" t="n">
-        <v>808278</v>
-      </c>
-      <c r="M29" t="n">
-        <v>15501</v>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>Error: Value cannot be null. (Parameter 'input')</t>
-        </is>
-      </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>Error: Value cannot be null. (Parameter 'input')</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>Mangler gyldig merke/sekvens; Representant mangler gyldig merkekilde; Mangler rominfo</t>
-        </is>
-      </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>Autodesk Docs://Fornebubanen/U_F_BAS_FBU_RIE_XXX.rvt</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>5e8f81e4-fcff-4378-8a08-70d893e9ab6c-0110f8e2</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>BAS-300-C3S02</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Segment</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>12351764</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>12351767</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>5f883497-5a39-4b7c-b120-6b279b0b6c8e-00bb3300</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>5f883497-5a39-4b7c-b120-6b279b0b6c8e-00bb31fa</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Kabelstige 300 mm x 60 mm</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="I30" t="n">
-        <v>300</v>
-      </c>
-      <c r="J30" t="n">
-        <v>60</v>
-      </c>
-      <c r="K30" t="n">
-        <v>808279</v>
-      </c>
-      <c r="L30" t="n">
-        <v>808279</v>
-      </c>
-      <c r="M30" t="n">
-        <v>15501</v>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>Error: Value cannot be null. (Parameter 'input')</t>
-        </is>
-      </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>Error: Value cannot be null. (Parameter 'input')</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>Mangler gyldig merke/sekvens; Representant mangler gyldig merkekilde; Mangler rominfo</t>
-        </is>
-      </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>Autodesk Docs://Fornebubanen/U_F_BAS_FBU_RIE_XXX.rvt</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>5e8f81e4-fcff-4378-8a08-70d893e9ab6c-0110f8e2</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>BAS-300-C3S02</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Segment</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>12351764</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>12351769</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>5f883497-5a39-4b7c-b120-6b279b0b6c8e-00bb338a</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>5f883497-5a39-4b7c-b120-6b279b0b6c8e-00bb31fa</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Kabelstige 300 mm x 60 mm</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="I31" t="n">
-        <v>300</v>
-      </c>
-      <c r="J31" t="n">
-        <v>60</v>
-      </c>
-      <c r="K31" t="n">
-        <v>808280</v>
-      </c>
-      <c r="L31" t="n">
-        <v>808280</v>
-      </c>
-      <c r="M31" t="n">
-        <v>15501</v>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>Error: Value cannot be null. (Parameter 'input')</t>
-        </is>
-      </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>Error: Value cannot be null. (Parameter 'input')</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>Mangler gyldig merke/sekvens; Representant mangler gyldig merkekilde; Mangler rominfo</t>
-        </is>
-      </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>Autodesk Docs://Fornebubanen/U_F_BAS_FBU_RIE_XXX.rvt</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>5e8f81e4-fcff-4378-8a08-70d893e9ab6c-0110f8e2</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>BAS-300-C3S02</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Segment</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>12351764</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>12351771</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>5f883497-5a39-4b7c-b120-6b279b0b6c8e-00bb3441</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>5f883497-5a39-4b7c-b120-6b279b0b6c8e-00bb31fa</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Kabelstige 300 mm x 60 mm</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="I32" t="n">
-        <v>300</v>
-      </c>
-      <c r="J32" t="n">
-        <v>60</v>
-      </c>
-      <c r="K32" t="n">
-        <v>808281</v>
-      </c>
-      <c r="L32" t="n">
-        <v>808281</v>
-      </c>
-      <c r="M32" t="n">
-        <v>15501</v>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>Error: Value cannot be null. (Parameter 'input')</t>
-        </is>
-      </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>Error: Value cannot be null. (Parameter 'input')</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>Mangler gyldig merke/sekvens; Representant mangler gyldig merkekilde; Mangler rominfo</t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>Autodesk Docs://Fornebubanen/U_F_BAS_FBU_RIE_XXX.rvt</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>5e8f81e4-fcff-4378-8a08-70d893e9ab6c-0110f8e2</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>BAS-300-C3S02</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Segment</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>12351764</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>12351773</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>5f883497-5a39-4b7c-b120-6b279b0b6c8e-00bb3514</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>5f883497-5a39-4b7c-b120-6b279b0b6c8e-00bb31fa</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Kabelstige 300 mm x 60 mm</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="I33" t="n">
-        <v>300</v>
-      </c>
-      <c r="J33" t="n">
-        <v>60</v>
-      </c>
-      <c r="K33" t="n">
-        <v>808282</v>
-      </c>
-      <c r="L33" t="n">
-        <v>808282</v>
-      </c>
-      <c r="M33" t="n">
-        <v>15501</v>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>Error: Value cannot be null. (Parameter 'input')</t>
-        </is>
-      </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>Error: Value cannot be null. (Parameter 'input')</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>Mangler gyldig merke/sekvens; Representant mangler gyldig merkekilde; Mangler rominfo</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>Autodesk Docs://Fornebubanen/U_F_BAS_FBU_RIE_XXX.rvt</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>5e8f81e4-fcff-4378-8a08-70d893e9ab6c-0110f8e2</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>BAS-600-C3S02</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Segment</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>12262924</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>12351754</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>5f883497-5a39-4b7c-b120-6b279b0b6c8e-00bb2d2b</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>3de28406-8391-46ef-a35b-32becf36f03e-00bb1e0c</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Kabelstige 600 mm x 60 mm</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="I34" t="n">
-        <v>600</v>
-      </c>
-      <c r="J34" t="n">
-        <v>60</v>
-      </c>
-      <c r="K34" t="n">
-        <v>809079</v>
-      </c>
-      <c r="L34" t="n">
-        <v>809079</v>
-      </c>
-      <c r="M34" t="n">
-        <v>15499</v>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>Error: Value cannot be null. (Parameter 'input')</t>
-        </is>
-      </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>BYG201-460-KAF-326</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>326</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>C3S.02</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>Mangler gyldig merke/sekvens; Merke/sekvens avviker fra representant; Mangler rominfo</t>
-        </is>
-      </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>Autodesk Docs://Fornebubanen/U_F_BAS_FBU_RIE_XXX.rvt</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>5e8f81e4-fcff-4378-8a08-70d893e9ab6c-0110f8e2</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>BAS-600-C3S02</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Segment</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>12262924</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>12351756</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>5f883497-5a39-4b7c-b120-6b279b0b6c8e-00bb2df1</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>3de28406-8391-46ef-a35b-32becf36f03e-00bb1e0c</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Kabelstige 600 mm x 60 mm</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="I35" t="n">
-        <v>600</v>
-      </c>
-      <c r="J35" t="n">
-        <v>60</v>
-      </c>
-      <c r="K35" t="n">
-        <v>809080</v>
-      </c>
-      <c r="L35" t="n">
-        <v>809080</v>
-      </c>
-      <c r="M35" t="n">
-        <v>15499</v>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>Error: Value cannot be null. (Parameter 'input')</t>
-        </is>
-      </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>BYG201-460-KAF-326</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>326</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>C3S.02</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>Mangler gyldig merke/sekvens; Merke/sekvens avviker fra representant; Mangler rominfo</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>Autodesk Docs://Fornebubanen/U_F_BAS_FBU_RIE_XXX.rvt</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>5e8f81e4-fcff-4378-8a08-70d893e9ab6c-0110f8e2</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>BAS-600-C3S02</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Segment</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>12262924</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>12351758</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>5f883497-5a39-4b7c-b120-6b279b0b6c8e-00bb2f89</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>3de28406-8391-46ef-a35b-32becf36f03e-00bb1e0c</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Kabelstige 600 mm x 60 mm</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="I36" t="n">
-        <v>600</v>
-      </c>
-      <c r="J36" t="n">
-        <v>60</v>
-      </c>
-      <c r="K36" t="n">
-        <v>809081</v>
-      </c>
-      <c r="L36" t="n">
-        <v>809081</v>
-      </c>
-      <c r="M36" t="n">
-        <v>15499</v>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>Error: Value cannot be null. (Parameter 'input')</t>
-        </is>
-      </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>BYG201-460-KAF-326</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>326</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>C3S.02</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>Mangler gyldig merke/sekvens; Merke/sekvens avviker fra representant; Mangler rominfo</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>Autodesk Docs://Fornebubanen/U_F_BAS_FBU_RIE_XXX.rvt</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>5e8f81e4-fcff-4378-8a08-70d893e9ab6c-0110f8e2</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>BAS-600-C3S02</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Segment</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>12262924</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>12351760</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>5f883497-5a39-4b7c-b120-6b279b0b6c8e-00bb3013</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>3de28406-8391-46ef-a35b-32becf36f03e-00bb1e0c</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Kabelstige 600 mm x 60 mm</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="I37" t="n">
-        <v>600</v>
-      </c>
-      <c r="J37" t="n">
-        <v>60</v>
-      </c>
-      <c r="K37" t="n">
-        <v>809082</v>
-      </c>
-      <c r="L37" t="n">
-        <v>809082</v>
-      </c>
-      <c r="M37" t="n">
-        <v>15499</v>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>Error: Value cannot be null. (Parameter 'input')</t>
-        </is>
-      </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>BYG201-460-KAF-326</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>326</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>C3S.02</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>Mangler gyldig merke/sekvens; Merke/sekvens avviker fra representant; Mangler rominfo</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>Autodesk Docs://Fornebubanen/U_F_BAS_FBU_RIE_XXX.rvt</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>5e8f81e4-fcff-4378-8a08-70d893e9ab6c-0110f8e2</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>BAS-7293888</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Segment</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>7293888</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>12782333</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>3a927da6-68d6-46e3-b38d-cfd5fd3d39ec-00c30afd</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>b5f1e081-d2e1-4cf0-aa45-eddfa811166a-006f4bc0</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Kabelstige 300 mm x 60 mm</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="I38" t="n">
-        <v>300</v>
-      </c>
-      <c r="J38" t="n">
-        <v>60</v>
-      </c>
-      <c r="K38" t="n">
-        <v>808302</v>
-      </c>
-      <c r="L38" t="n">
-        <v>808302</v>
-      </c>
-      <c r="M38" t="n">
-        <v>15501</v>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>BYG202-460-KAF-319</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>319</t>
-        </is>
-      </c>
-      <c r="Q38" t="n">
-        <v>3850</v>
-      </c>
-      <c r="R38" t="inlineStr">
-        <is>
-          <t>L3S.02</t>
-        </is>
-      </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>Innkjøring</t>
-        </is>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>BYG202-460-KAF-230</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>L3S.02</t>
-        </is>
-      </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>Merke/sekvens avviker fra representant</t>
-        </is>
-      </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>Autodesk Docs://Fornebubanen/U_F_BAS_FBU_RIE_XXX.rvt</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>5e8f81e4-fcff-4378-8a08-70d893e9ab6c-0110f8e2</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>BAS-7293888</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Segment</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>7293888</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>7188755</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>c3deda7f-f73a-474c-8b0a-0005790653d8-006db113</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>b5f1e081-d2e1-4cf0-aa45-eddfa811166a-006f4bc0</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Kabelstige 300 mm x 60 mm</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="I39" t="n">
-        <v>300</v>
-      </c>
-      <c r="J39" t="n">
-        <v>60</v>
-      </c>
-      <c r="K39" t="n">
-        <v>807848</v>
-      </c>
-      <c r="L39" t="n">
-        <v>807848</v>
-      </c>
-      <c r="M39" t="n">
-        <v>15501</v>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>BYG202-460-KAF-229</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>229</t>
-        </is>
-      </c>
-      <c r="Q39" t="n">
-        <v>3850</v>
-      </c>
-      <c r="R39" t="inlineStr">
-        <is>
-          <t>L3S.02</t>
-        </is>
-      </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>Innkjøring</t>
-        </is>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>BYG202-460-KAF-230</t>
-        </is>
-      </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>L3S.02</t>
-        </is>
-      </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>Merke/sekvens avviker fra representant</t>
-        </is>
-      </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>Autodesk Docs://Fornebubanen/U_F_BAS_FBU_RIE_XXX.rvt</t>
-        </is>
-      </c>
-      <c r="Y39" t="inlineStr">
-        <is>
-          <t>5e8f81e4-fcff-4378-8a08-70d893e9ab6c-0110f8e2</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>BAS-7293888</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Segment</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>7293888</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>7294217</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>b5f1e081-d2e1-4cf0-aa45-eddfa811166a-006f4d09</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>b5f1e081-d2e1-4cf0-aa45-eddfa811166a-006f4bc0</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Kabelstige 300 mm x 60 mm</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="I40" t="n">
-        <v>300</v>
-      </c>
-      <c r="J40" t="n">
-        <v>60</v>
-      </c>
-      <c r="K40" t="n">
-        <v>807854</v>
-      </c>
-      <c r="L40" t="n">
-        <v>807854</v>
-      </c>
-      <c r="M40" t="n">
-        <v>15501</v>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>BYG202-460-KAF-231</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
-      <c r="Q40" t="n">
-        <v>3850</v>
-      </c>
-      <c r="R40" t="inlineStr">
-        <is>
-          <t>L3S.02</t>
-        </is>
-      </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>Innkjøring</t>
-        </is>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>BYG202-460-KAF-230</t>
-        </is>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>L3S.02</t>
-        </is>
-      </c>
-      <c r="W40" t="inlineStr">
-        <is>
-          <t>Merke/sekvens avviker fra representant</t>
-        </is>
-      </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>Autodesk Docs://Fornebubanen/U_F_BAS_FBU_RIE_XXX.rvt</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr">
-        <is>
-          <t>5e8f81e4-fcff-4378-8a08-70d893e9ab6c-0110f8e2</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>BAS-7293888</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Segment</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>7293888</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>7294314</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>b5f1e081-d2e1-4cf0-aa45-eddfa811166a-006f4d6a</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>b5f1e081-d2e1-4cf0-aa45-eddfa811166a-006f4bc0</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Kabelstige 300 mm x 60 mm</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="I41" t="n">
-        <v>300</v>
-      </c>
-      <c r="J41" t="n">
-        <v>60</v>
-      </c>
-      <c r="K41" t="n">
-        <v>807855</v>
-      </c>
-      <c r="L41" t="n">
-        <v>807855</v>
-      </c>
-      <c r="M41" t="n">
-        <v>15501</v>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>BYG202-460-KAF-232</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="Q41" t="n">
-        <v>3850</v>
-      </c>
-      <c r="R41" t="inlineStr">
-        <is>
-          <t>L3S.02</t>
-        </is>
-      </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>Innkjøring</t>
-        </is>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>BYG202-460-KAF-230</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>L3S.02</t>
-        </is>
-      </c>
-      <c r="W41" t="inlineStr">
-        <is>
-          <t>Merke/sekvens avviker fra representant</t>
-        </is>
-      </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>Autodesk Docs://Fornebubanen/U_F_BAS_FBU_RIE_XXX.rvt</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>5e8f81e4-fcff-4378-8a08-70d893e9ab6c-0110f8e2</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>BAS-7293888</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Segment</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>7293888</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>8100708</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>6276c923-1b2b-4399-98db-180fd064a4a8-007b9b64</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>b5f1e081-d2e1-4cf0-aa45-eddfa811166a-006f4bc0</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Kabelstige 300 mm x 60 mm</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="I42" t="n">
-        <v>300</v>
-      </c>
-      <c r="J42" t="n">
-        <v>60</v>
-      </c>
-      <c r="K42" t="n">
-        <v>807938</v>
-      </c>
-      <c r="L42" t="n">
-        <v>807938</v>
-      </c>
-      <c r="M42" t="n">
-        <v>15501</v>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>BYG202-460-KAF-242</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
-      <c r="Q42" t="n">
-        <v>3850</v>
-      </c>
-      <c r="R42" t="inlineStr">
-        <is>
-          <t>L3S.02</t>
-        </is>
-      </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>Innkjøring</t>
-        </is>
-      </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>BYG202-460-KAF-230</t>
-        </is>
-      </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>L3S.02</t>
-        </is>
-      </c>
-      <c r="W42" t="inlineStr">
-        <is>
-          <t>Merke/sekvens avviker fra representant</t>
-        </is>
-      </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>Autodesk Docs://Fornebubanen/U_F_BAS_FBU_RIE_XXX.rvt</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>5e8f81e4-fcff-4378-8a08-70d893e9ab6c-0110f8e2</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>BAS-7788672</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Segment</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>7788672</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>7788544</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>faac82b0-456e-4a8c-b7e3-8c5e721d51cb-0076d800</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>a8bbcf38-e0eb-42e8-bb3c-2ead6cb6fcfa-0076d880</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Kabelstige 300 mm x 60 mm</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="I43" t="n">
-        <v>300</v>
-      </c>
-      <c r="J43" t="n">
-        <v>60</v>
-      </c>
-      <c r="K43" t="n">
-        <v>807898</v>
-      </c>
-      <c r="L43" t="n">
-        <v>807898</v>
-      </c>
-      <c r="M43" t="n">
-        <v>15501</v>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>BYG201-460-KAF-060</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>060</t>
-        </is>
-      </c>
-      <c r="Q43" t="n">
-        <v>2237</v>
-      </c>
-      <c r="R43" t="inlineStr">
-        <is>
-          <t>C3S.03</t>
-        </is>
-      </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>Nordøst 7</t>
-        </is>
-      </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>BYG201-460-KAF-062</t>
-        </is>
-      </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>062</t>
-        </is>
-      </c>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>C3S.03</t>
-        </is>
-      </c>
-      <c r="W43" t="inlineStr">
-        <is>
-          <t>Merke/sekvens avviker fra representant</t>
-        </is>
-      </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>Autodesk Docs://Fornebubanen/U_F_BAS_FBU_RIE_XXX.rvt</t>
-        </is>
-      </c>
-      <c r="Y43" t="inlineStr">
-        <is>
-          <t>5e8f81e4-fcff-4378-8a08-70d893e9ab6c-0110f8e2</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>BAS-7788797</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Segment</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>7788797</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>15431238</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>e37bb007-7991-4863-9416-43e287aa5d72-00eb7646</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>a8bbcf38-e0eb-42e8-bb3c-2ead6cb6fcfa-0076d8fd</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Kabelstige 300 mm x 60 mm</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="I44" t="n">
-        <v>300</v>
-      </c>
-      <c r="J44" t="n">
-        <v>60</v>
-      </c>
-      <c r="K44" t="n">
-        <v>808581</v>
-      </c>
-      <c r="L44" t="n">
-        <v>808581</v>
-      </c>
-      <c r="M44" t="n">
-        <v>15501</v>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>BYG201-460-KAF-280</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>280</t>
-        </is>
-      </c>
-      <c r="Q44" t="n">
-        <v>2796</v>
-      </c>
-      <c r="R44" t="inlineStr">
-        <is>
-          <t>E3S.01</t>
-        </is>
-      </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>Spor P8-P9 nord</t>
-        </is>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>BYG201-460-KAF-063</t>
-        </is>
-      </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>063</t>
-        </is>
-      </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>E3S.01</t>
-        </is>
-      </c>
-      <c r="W44" t="inlineStr">
-        <is>
-          <t>Merke/sekvens avviker fra representant</t>
-        </is>
-      </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>Autodesk Docs://Fornebubanen/U_F_BAS_FBU_RIE_XXX.rvt</t>
-        </is>
-      </c>
-      <c r="Y44" t="inlineStr">
-        <is>
-          <t>5e8f81e4-fcff-4378-8a08-70d893e9ab6c-0110f8e2</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>BAS-7808088</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Segment</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>7808088</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>5090754</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>1bb32946-7542-4937-8b0b-b55b47dad3dd-004da4ac</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>d9591674-d193-4774-b266-166e555fee1c-00772458</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Kabelstige 400 mm x 60 mm</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="I45" t="n">
-        <v>400</v>
-      </c>
-      <c r="J45" t="n">
-        <v>60</v>
-      </c>
-      <c r="K45" t="n">
-        <v>807705</v>
-      </c>
-      <c r="L45" t="n">
-        <v>807705</v>
-      </c>
-      <c r="M45" t="n">
-        <v>15500</v>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>BYG201-460-KAF-011</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>011</t>
-        </is>
-      </c>
-      <c r="Q45" t="n">
-        <v>574</v>
-      </c>
-      <c r="R45" t="inlineStr">
-        <is>
-          <t>E8S.01</t>
-        </is>
-      </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>Sør</t>
-        </is>
-      </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>BYG201-460-KAF-072</t>
-        </is>
-      </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>072</t>
-        </is>
-      </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>E8S.01</t>
-        </is>
-      </c>
-      <c r="W45" t="inlineStr">
-        <is>
-          <t>Merke/sekvens avviker fra representant</t>
-        </is>
-      </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>Autodesk Docs://Fornebubanen/U_F_BAS_FBU_RIE_XXX.rvt</t>
-        </is>
-      </c>
-      <c r="Y45" t="inlineStr">
-        <is>
-          <t>5e8f81e4-fcff-4378-8a08-70d893e9ab6c-0110f8e2</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>BAS-8118032</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Segment</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>8118032</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>8118016</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>9a5c8b06-345a-4e39-bd03-252ff189fd84-007bdf00</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>9a5c8b06-345a-4e39-bd03-252ff189fd84-007bdf10</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Kabelstige 300 mm x 60 mm</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="I46" t="n">
-        <v>300</v>
-      </c>
-      <c r="J46" t="n">
-        <v>60</v>
-      </c>
-      <c r="K46" t="n">
-        <v>807940</v>
-      </c>
-      <c r="L46" t="n">
-        <v>807940</v>
-      </c>
-      <c r="M46" t="n">
-        <v>15501</v>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>P14-460-KAF-007</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>007</t>
-        </is>
-      </c>
-      <c r="Q46" t="n">
-        <v>4209</v>
-      </c>
-      <c r="R46" t="inlineStr">
-        <is>
-          <t>L4S.28</t>
-        </is>
-      </c>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>P14-460-KAF-008</t>
-        </is>
-      </c>
-      <c r="U46" t="inlineStr">
-        <is>
-          <t>008</t>
-        </is>
-      </c>
-      <c r="V46" t="inlineStr">
-        <is>
-          <t>L4S.28</t>
-        </is>
-      </c>
-      <c r="W46" t="inlineStr">
-        <is>
-          <t>Merke/sekvens avviker fra representant</t>
-        </is>
-      </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>Autodesk Docs://Fornebubanen/U_F_BAS_FBU_RIE_XXX.rvt</t>
-        </is>
-      </c>
-      <c r="Y46" t="inlineStr">
-        <is>
-          <t>5e8f81e4-fcff-4378-8a08-70d893e9ab6c-0110f8e2</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>BAS-8118032</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Segment</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>8118032</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>8118062</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>9a5c8b06-345a-4e39-bd03-252ff189fd84-007bdf2e</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>9a5c8b06-345a-4e39-bd03-252ff189fd84-007bdf10</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Kabelstige 300 mm x 60 mm</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="I47" t="n">
-        <v>300</v>
-      </c>
-      <c r="J47" t="n">
-        <v>60</v>
-      </c>
-      <c r="K47" t="n">
-        <v>807942</v>
-      </c>
-      <c r="L47" t="n">
-        <v>807942</v>
-      </c>
-      <c r="M47" t="n">
-        <v>15501</v>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>P14-460-KAF-009</t>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>009</t>
-        </is>
-      </c>
-      <c r="Q47" t="n">
-        <v>4209</v>
-      </c>
-      <c r="R47" t="inlineStr">
-        <is>
-          <t>L4S.28</t>
-        </is>
-      </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>P14-460-KAF-008</t>
-        </is>
-      </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>008</t>
-        </is>
-      </c>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>L4S.28</t>
-        </is>
-      </c>
-      <c r="W47" t="inlineStr">
-        <is>
-          <t>Merke/sekvens avviker fra representant</t>
-        </is>
-      </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>Autodesk Docs://Fornebubanen/U_F_BAS_FBU_RIE_XXX.rvt</t>
-        </is>
-      </c>
-      <c r="Y47" t="inlineStr">
-        <is>
-          <t>5e8f81e4-fcff-4378-8a08-70d893e9ab6c-0110f8e2</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>BAS-8577253</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Segment</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>8577253</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>15097600</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>f13071fd-e1cb-4586-8580-80adbb1594d9-00e65f00</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>a67473b7-99c9-4bc3-ad96-6d1518c05e9e-0082e0e5</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Kabelstige 600 mm x 60 mm</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="I48" t="n">
-        <v>600</v>
-      </c>
-      <c r="J48" t="n">
-        <v>60</v>
-      </c>
-      <c r="K48" t="n">
-        <v>809129</v>
-      </c>
-      <c r="L48" t="n">
-        <v>809129</v>
-      </c>
-      <c r="M48" t="n">
-        <v>15499</v>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>BYG202-460-KAF-409</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>409</t>
-        </is>
-      </c>
-      <c r="Q48" t="n">
-        <v>506</v>
-      </c>
-      <c r="R48" t="inlineStr">
-        <is>
-          <t>M3G1.02</t>
-        </is>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>BYG202-460-KAF-249</t>
-        </is>
-      </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>249</t>
-        </is>
-      </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>M3G1.02</t>
-        </is>
-      </c>
-      <c r="W48" t="inlineStr">
-        <is>
-          <t>Merke/sekvens avviker fra representant</t>
-        </is>
-      </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>Autodesk Docs://Fornebubanen/U_F_BAS_FBU_RIE_XXX.rvt</t>
-        </is>
-      </c>
-      <c r="Y48" t="inlineStr">
-        <is>
-          <t>5e8f81e4-fcff-4378-8a08-70d893e9ab6c-0110f8e2</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>BAS-9356349</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Segment</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>9356349</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>7513525</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>3d5a7e32-fb52-401d-b831-acb1f5b57d20-0072a5b5</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>55ec083c-7f8f-44f9-940c-a3375ca937f7-008ec43d</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Kabelstige 600 mm x 60 mm</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="I49" t="n">
-        <v>600</v>
-      </c>
-      <c r="J49" t="n">
-        <v>60</v>
-      </c>
-      <c r="K49" t="n">
-        <v>808963</v>
-      </c>
-      <c r="L49" t="n">
-        <v>808963</v>
-      </c>
-      <c r="M49" t="n">
-        <v>15499</v>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>BYG202-460-KAF-236</t>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
-      <c r="Q49" t="n">
-        <v>562</v>
-      </c>
-      <c r="R49" t="inlineStr">
-        <is>
-          <t>M3G2.03</t>
-        </is>
-      </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>Verkstedhall</t>
-        </is>
-      </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>BYG202-460-KAF-261</t>
-        </is>
-      </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>261</t>
-        </is>
-      </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>M3G2.03</t>
-        </is>
-      </c>
-      <c r="W49" t="inlineStr">
-        <is>
-          <t>Merke/sekvens avviker fra representant</t>
-        </is>
-      </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>Autodesk Docs://Fornebubanen/U_F_BAS_FBU_RIE_XXX.rvt</t>
-        </is>
-      </c>
-      <c r="Y49" t="inlineStr">
-        <is>
-          <t>5e8f81e4-fcff-4378-8a08-70d893e9ab6c-0110f8e2</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>BAS-9356349</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Segment</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>9356349</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>9356232</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>55ec083c-7f8f-44f9-940c-a3375ca937f7-008ec3c8</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>55ec083c-7f8f-44f9-940c-a3375ca937f7-008ec43d</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Kabelstige 600 mm x 60 mm</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="I50" t="n">
-        <v>600</v>
-      </c>
-      <c r="J50" t="n">
-        <v>60</v>
-      </c>
-      <c r="K50" t="n">
-        <v>809019</v>
-      </c>
-      <c r="L50" t="n">
-        <v>809019</v>
-      </c>
-      <c r="M50" t="n">
-        <v>15499</v>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>BYG202-460-KAF-260</t>
-        </is>
-      </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>260</t>
-        </is>
-      </c>
-      <c r="Q50" t="n">
-        <v>562</v>
-      </c>
-      <c r="R50" t="inlineStr">
-        <is>
-          <t>M3G2.03</t>
-        </is>
-      </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>Verkstedhall</t>
-        </is>
-      </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>BYG202-460-KAF-261</t>
-        </is>
-      </c>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>261</t>
-        </is>
-      </c>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>M3G2.03</t>
-        </is>
-      </c>
-      <c r="W50" t="inlineStr">
-        <is>
-          <t>Merke/sekvens avviker fra representant</t>
-        </is>
-      </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>Autodesk Docs://Fornebubanen/U_F_BAS_FBU_RIE_XXX.rvt</t>
-        </is>
-      </c>
-      <c r="Y50" t="inlineStr">
-        <is>
-          <t>5e8f81e4-fcff-4378-8a08-70d893e9ab6c-0110f8e2</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>BAS-9356413</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Segment</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>9356413</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>17483491</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>4ad1b7f0-f3ce-4589-831d-0bf2df01d6ac-010ac6e3</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>55ec083c-7f8f-44f9-940c-a3375ca937f7-008ec47d</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Kabelstige 800 mm x 60 mm</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="I51" t="n">
-        <v>800</v>
-      </c>
-      <c r="J51" t="n">
-        <v>60</v>
-      </c>
-      <c r="K51" t="n">
-        <v>808774</v>
-      </c>
-      <c r="L51" t="n">
-        <v>808774</v>
-      </c>
-      <c r="M51" t="n">
-        <v>16281</v>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>BYG202-460-KAF-443</t>
-        </is>
-      </c>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>443</t>
-        </is>
-      </c>
-      <c r="Q51" t="n">
-        <v>562</v>
-      </c>
-      <c r="R51" t="inlineStr">
-        <is>
-          <t>M3G2.03</t>
-        </is>
-      </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>Verkstedhall</t>
-        </is>
-      </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>BYG202-460-KAF-262</t>
-        </is>
-      </c>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
-      </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>M3G2.03</t>
-        </is>
-      </c>
-      <c r="W51" t="inlineStr">
-        <is>
-          <t>Merke/sekvens avviker fra representant</t>
-        </is>
-      </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>Autodesk Docs://Fornebubanen/U_F_BAS_FBU_RIE_XXX.rvt</t>
-        </is>
-      </c>
-      <c r="Y51" t="inlineStr">
-        <is>
-          <t>5e8f81e4-fcff-4378-8a08-70d893e9ab6c-0110f8e2</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>BAS-9356413</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Segment</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>9356413</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>17483581</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>4ad1b7f0-f3ce-4589-831d-0bf2df01d6ac-010ac73d</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>55ec083c-7f8f-44f9-940c-a3375ca937f7-008ec47d</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Kabelstige 800 mm x 60 mm</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="I52" t="n">
-        <v>800</v>
-      </c>
-      <c r="J52" t="n">
-        <v>60</v>
-      </c>
-      <c r="K52" t="n">
-        <v>808775</v>
-      </c>
-      <c r="L52" t="n">
-        <v>808775</v>
-      </c>
-      <c r="M52" t="n">
-        <v>16281</v>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>BYG202-460-KAF-444</t>
-        </is>
-      </c>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>444</t>
-        </is>
-      </c>
-      <c r="Q52" t="n">
-        <v>3850</v>
-      </c>
-      <c r="R52" t="inlineStr">
-        <is>
-          <t>L3S.02</t>
-        </is>
-      </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>Innkjøring</t>
-        </is>
-      </c>
-      <c r="T52" t="inlineStr">
-        <is>
-          <t>BYG202-460-KAF-262</t>
-        </is>
-      </c>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
-      </c>
-      <c r="V52" t="inlineStr">
-        <is>
-          <t>M3G2.03</t>
-        </is>
-      </c>
-      <c r="W52" t="inlineStr">
-        <is>
-          <t>Merke/sekvens avviker fra representant; Rominfo avviker – avklar</t>
-        </is>
-      </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>Autodesk Docs://Fornebubanen/U_F_BAS_FBU_RIE_XXX.rvt</t>
-        </is>
-      </c>
-      <c r="Y52" t="inlineStr">
-        <is>
-          <t>5e8f81e4-fcff-4378-8a08-70d893e9ab6c-0110f8e2</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>BAS-9356413</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Segment</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>9356413</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>17483715</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>4ad1b7f0-f3ce-4589-831d-0bf2df01d6ac-010ac7c3</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>55ec083c-7f8f-44f9-940c-a3375ca937f7-008ec47d</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Kabelstige 800 mm x 60 mm</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="I53" t="n">
-        <v>800</v>
-      </c>
-      <c r="J53" t="n">
-        <v>60</v>
-      </c>
-      <c r="K53" t="n">
-        <v>808776</v>
-      </c>
-      <c r="L53" t="n">
-        <v>808776</v>
-      </c>
-      <c r="M53" t="n">
-        <v>16281</v>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>BYG202-460-KAF-445</t>
-        </is>
-      </c>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>445</t>
-        </is>
-      </c>
-      <c r="Q53" t="n">
-        <v>3850</v>
-      </c>
-      <c r="R53" t="inlineStr">
-        <is>
-          <t>L3S.02</t>
-        </is>
-      </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>Innkjøring</t>
-        </is>
-      </c>
-      <c r="T53" t="inlineStr">
-        <is>
-          <t>BYG202-460-KAF-262</t>
-        </is>
-      </c>
-      <c r="U53" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
-      </c>
-      <c r="V53" t="inlineStr">
-        <is>
-          <t>M3G2.03</t>
-        </is>
-      </c>
-      <c r="W53" t="inlineStr">
-        <is>
-          <t>Merke/sekvens avviker fra representant; Rominfo avviker – avklar</t>
-        </is>
-      </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>Autodesk Docs://Fornebubanen/U_F_BAS_FBU_RIE_XXX.rvt</t>
-        </is>
-      </c>
-      <c r="Y53" t="inlineStr">
-        <is>
-          <t>5e8f81e4-fcff-4378-8a08-70d893e9ab6c-0110f8e2</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>BAS-9906788</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Segment</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>9906788</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>7913151</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>327fce30-3519-42d6-a7e1-57e1ecd99bc6-0078bebf</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>18fa763f-02ee-4055-a811-c0110f396833-00972a64</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Kabelstige 300 mm x 60 mm</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="I54" t="n">
-        <v>300</v>
-      </c>
-      <c r="J54" t="n">
-        <v>60</v>
-      </c>
-      <c r="K54" t="n">
-        <v>807916</v>
-      </c>
-      <c r="L54" t="n">
-        <v>807916</v>
-      </c>
-      <c r="M54" t="n">
-        <v>15501</v>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="O54" t="inlineStr">
-        <is>
-          <t>BYG203-460-KAF-062</t>
-        </is>
-      </c>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>062</t>
-        </is>
-      </c>
-      <c r="Q54" t="n">
-        <v>1918</v>
-      </c>
-      <c r="R54" t="inlineStr">
-        <is>
-          <t>L4U2.06</t>
-        </is>
-      </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>Varemottak</t>
-        </is>
-      </c>
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>BYG203-460-KAF-068</t>
-        </is>
-      </c>
-      <c r="U54" t="inlineStr">
-        <is>
-          <t>068</t>
-        </is>
-      </c>
-      <c r="V54" t="inlineStr">
-        <is>
-          <t>L4U2.06</t>
-        </is>
-      </c>
-      <c r="W54" t="inlineStr">
-        <is>
-          <t>Merke/sekvens avviker fra representant</t>
-        </is>
-      </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>Autodesk Docs://Fornebubanen/U_F_BAS_FBU_RIE_XXX.rvt</t>
-        </is>
-      </c>
-      <c r="Y54" t="inlineStr">
         <is>
           <t>5e8f81e4-fcff-4378-8a08-70d893e9ab6c-0110f8e2</t>
         </is>

--- a/config/DrofusConfirmedRoutes.xlsx
+++ b/config/DrofusConfirmedRoutes.xlsx
@@ -558,7 +558,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>D:\Revit\Python\Revit_BIM_Agent\logs\reports\BAS strekk samordning 20261016_1450 remaining Verify confirmed.tsv</t>
+          <t>D:\Revit\Python\Revit_BIM_Agent\logs\reports\BAS strekk samordning 20261016_151911 Verify confirmed.tsv</t>
         </is>
       </c>
     </row>
@@ -570,7 +570,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-16T14:57:12</t>
+          <t>2026-10-16T15:20:32</t>
         </is>
       </c>
     </row>

--- a/config/DrofusConfirmedRoutes.xlsx
+++ b/config/DrofusConfirmedRoutes.xlsx
@@ -558,7 +558,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>D:\Revit\Python\Revit_BIM_Agent\logs\reports\BAS strekk samordning 20261016_151911 Verify confirmed.tsv</t>
+          <t>D:\Revit\Python\Revit_BIM_Agent\logs\reports\BAS bekreftede strekk snapshot 20261016_153034.tsv</t>
         </is>
       </c>
     </row>
@@ -570,7 +570,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-16T15:20:32</t>
+          <t>2026-10-16T15:41:50</t>
         </is>
       </c>
     </row>
